--- a/B/chrIII:135694-180925_30_finemapping.xlsx
+++ b/B/chrIII:135694-180925_30_finemapping.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3972" uniqueCount="3972">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3964" uniqueCount="3964">
   <si>
     <t xml:space="preserve">DATA</t>
   </si>
@@ -10733,19 +10733,10 @@
     <t xml:space="preserve">in.hotspot</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.x</t>
-  </si>
-  <si>
     <t xml:space="preserve">bin_pos_l</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.y</t>
+    <t xml:space="preserve">SE</t>
   </si>
   <si>
     <t xml:space="preserve">chrom_short</t>
@@ -11049,21 +11040,6 @@
   </si>
   <si>
     <t xml:space="preserve">HXT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G2:M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_M:G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1:S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_S</t>
   </si>
   <si>
     <t xml:space="preserve">cis_fdr</t>
@@ -12366,48 +12342,42 @@
         <v>3569</v>
       </c>
       <c r="Z1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA1" t="s">
         <v>3570</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>3571</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>3572</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE1" t="s">
         <v>3573</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>3574</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>3575</v>
       </c>
-      <c r="AF1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>3576</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>3577</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>3578</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>3579</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>3581</v>
+        <v>3578</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -12461,62 +12431,60 @@
         <v>164068</v>
       </c>
       <c r="U2" t="s">
-        <v>3582</v>
+        <v>3579</v>
       </c>
       <c r="V2" t="n">
         <v>82580</v>
       </c>
       <c r="W2" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X2" t="b">
         <v>1</v>
       </c>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="Y2" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z2" t="n">
         <v>0.352517092642531</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AA2" t="n">
         <v>0.0329652160268363</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>3582</v>
       </c>
       <c r="AD2" t="s">
         <v>19</v>
       </c>
       <c r="AE2" t="s">
-        <v>3585</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>3585</v>
-      </c>
-      <c r="AH2" t="n">
+        <v>3582</v>
+      </c>
+      <c r="AF2" t="n">
         <v>2</v>
       </c>
-      <c r="AI2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>3586</v>
+      <c r="AG2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>3583</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>3587</v>
+        <v>3584</v>
       </c>
       <c r="D3" t="s">
-        <v>3588</v>
+        <v>3585</v>
       </c>
       <c r="E3" t="n">
         <v>167336</v>
@@ -12567,62 +12535,60 @@
         <v>173853</v>
       </c>
       <c r="U3" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="V3" t="n">
         <v>344671</v>
       </c>
       <c r="W3" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X3" t="b">
         <v>1</v>
       </c>
-      <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="Y3" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z3" t="n">
         <v>-0.39775786142837</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AA3" t="n">
         <v>0.0467994032407469</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>3587</v>
       </c>
       <c r="AD3" t="s">
         <v>19</v>
       </c>
       <c r="AE3" t="s">
-        <v>3590</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>3590</v>
-      </c>
-      <c r="AH3" t="n">
+        <v>3587</v>
+      </c>
+      <c r="AF3" t="n">
         <v>6</v>
       </c>
-      <c r="AI3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>3591</v>
+      <c r="AG3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>3588</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>3592</v>
+        <v>3589</v>
       </c>
       <c r="D4" t="s">
-        <v>3593</v>
+        <v>3590</v>
       </c>
       <c r="E4" t="n">
         <v>162941</v>
@@ -12673,59 +12639,57 @@
         <v>163645</v>
       </c>
       <c r="U4" t="s">
-        <v>3594</v>
+        <v>3591</v>
       </c>
       <c r="V4" t="n">
         <v>228771</v>
       </c>
       <c r="W4" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X4" t="b">
         <v>1</v>
       </c>
-      <c r="Y4"/>
-      <c r="Z4"/>
-      <c r="AA4" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="Y4" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z4" t="n">
         <v>-0.966013132002744</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AA4" t="n">
         <v>0.134745449036344</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>3592</v>
       </c>
       <c r="AD4" t="s">
         <v>19</v>
       </c>
       <c r="AE4" t="s">
-        <v>3595</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>3595</v>
-      </c>
-      <c r="AH4" t="n">
+        <v>3592</v>
+      </c>
+      <c r="AF4" t="n">
         <v>6</v>
       </c>
-      <c r="AI4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>3596</v>
+      <c r="AG4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>3593</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>3597</v>
+        <v>3594</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -12779,62 +12743,60 @@
         <v>164068</v>
       </c>
       <c r="U5" t="s">
-        <v>3598</v>
+        <v>3595</v>
       </c>
       <c r="V5" t="n">
         <v>352414</v>
       </c>
       <c r="W5" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X5" t="b">
         <v>1</v>
       </c>
-      <c r="Y5"/>
-      <c r="Z5"/>
-      <c r="AA5" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="Y5" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z5" t="n">
         <v>0.253328047590562</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AA5" t="n">
         <v>0.0296135643204784</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>3596</v>
       </c>
       <c r="AD5" t="s">
         <v>19</v>
       </c>
       <c r="AE5" t="s">
-        <v>3599</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>3599</v>
-      </c>
-      <c r="AH5" t="n">
+        <v>3596</v>
+      </c>
+      <c r="AF5" t="n">
         <v>2</v>
       </c>
-      <c r="AI5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>3600</v>
+      <c r="AG5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>3597</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>3601</v>
+        <v>3598</v>
       </c>
       <c r="D6" t="s">
-        <v>3588</v>
+        <v>3585</v>
       </c>
       <c r="E6" t="n">
         <v>173853</v>
@@ -12885,59 +12847,57 @@
         <v>173853</v>
       </c>
       <c r="U6" t="s">
-        <v>3602</v>
+        <v>3599</v>
       </c>
       <c r="V6" t="n">
         <v>442789</v>
       </c>
       <c r="W6" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X6" t="b">
         <v>1</v>
       </c>
-      <c r="Y6"/>
-      <c r="Z6"/>
-      <c r="AA6" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="Y6" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z6" t="n">
         <v>-0.709560617866188</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AA6" t="n">
         <v>0.109156706620477</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>3600</v>
       </c>
       <c r="AD6" t="s">
         <v>19</v>
       </c>
       <c r="AE6" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AH6" t="n">
+        <v>3600</v>
+      </c>
+      <c r="AF6" t="n">
         <v>6</v>
       </c>
-      <c r="AI6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>3604</v>
+      <c r="AG6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>3601</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>3605</v>
+        <v>3602</v>
       </c>
       <c r="D7" t="s">
         <v>63</v>
@@ -12991,62 +12951,60 @@
         <v>162941</v>
       </c>
       <c r="U7" t="s">
-        <v>3606</v>
+        <v>3603</v>
       </c>
       <c r="V7" t="n">
         <v>28583</v>
       </c>
       <c r="W7" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X7" t="b">
         <v>1</v>
       </c>
-      <c r="Y7"/>
-      <c r="Z7"/>
-      <c r="AA7" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="Y7" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z7" t="n">
         <v>-0.184349552825361</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AA7" t="n">
         <v>0.0254428482466538</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>3604</v>
       </c>
       <c r="AD7" t="s">
         <v>19</v>
       </c>
       <c r="AE7" t="s">
-        <v>3607</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>3607</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>3608</v>
+        <v>3604</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>3605</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>3609</v>
+        <v>3606</v>
       </c>
       <c r="D8" t="s">
-        <v>3610</v>
+        <v>3607</v>
       </c>
       <c r="E8" t="n">
         <v>164068</v>
@@ -13097,59 +13055,57 @@
         <v>170363</v>
       </c>
       <c r="U8" t="s">
-        <v>3602</v>
+        <v>3599</v>
       </c>
       <c r="V8" t="n">
         <v>526764</v>
       </c>
       <c r="W8" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X8" t="b">
         <v>1</v>
       </c>
-      <c r="Y8"/>
-      <c r="Z8"/>
-      <c r="AA8" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="Y8" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z8" t="n">
         <v>-0.373700028238208</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AA8" t="n">
         <v>0.0647756969473792</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>3600</v>
       </c>
       <c r="AD8" t="s">
         <v>19</v>
       </c>
       <c r="AE8" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AH8" t="n">
+        <v>3600</v>
+      </c>
+      <c r="AF8" t="n">
         <v>7</v>
       </c>
-      <c r="AI8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>3611</v>
+      <c r="AG8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>3608</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>3612</v>
+        <v>3609</v>
       </c>
       <c r="D9" t="s">
         <v>63</v>
@@ -13203,59 +13159,57 @@
         <v>162941</v>
       </c>
       <c r="U9" t="s">
-        <v>3613</v>
+        <v>3610</v>
       </c>
       <c r="V9" t="n">
         <v>1385176</v>
       </c>
       <c r="W9" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X9" t="b">
         <v>1</v>
       </c>
-      <c r="Y9"/>
-      <c r="Z9"/>
-      <c r="AA9" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="Y9" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z9" t="n">
         <v>0.228135947975972</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AA9" t="n">
         <v>0.0311434928516441</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>3611</v>
       </c>
       <c r="AD9" t="s">
         <v>19</v>
       </c>
       <c r="AE9" t="s">
-        <v>3614</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>3614</v>
-      </c>
-      <c r="AH9" t="n">
+        <v>3611</v>
+      </c>
+      <c r="AF9" t="n">
         <v>3</v>
       </c>
-      <c r="AI9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>3615</v>
+      <c r="AG9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>3612</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>3616</v>
+        <v>3613</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
@@ -13309,62 +13263,60 @@
         <v>164068</v>
       </c>
       <c r="U10" t="s">
-        <v>3617</v>
+        <v>3614</v>
       </c>
       <c r="V10" t="n">
         <v>42303</v>
       </c>
       <c r="W10" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X10" t="b">
         <v>1</v>
       </c>
-      <c r="Y10"/>
-      <c r="Z10"/>
-      <c r="AA10" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="Y10" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z10" t="n">
         <v>0.381354222066854</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AA10" t="n">
         <v>0.0640658114777122</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>3615</v>
       </c>
       <c r="AD10" t="s">
         <v>19</v>
       </c>
       <c r="AE10" t="s">
-        <v>3618</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>3618</v>
-      </c>
-      <c r="AH10" t="n">
+        <v>3615</v>
+      </c>
+      <c r="AF10" t="n">
         <v>0</v>
       </c>
-      <c r="AI10" t="b">
+      <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AJ10" t="s">
-        <v>3619</v>
+      <c r="AH10" t="s">
+        <v>3616</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>3620</v>
+        <v>3617</v>
       </c>
       <c r="D11" t="s">
-        <v>3610</v>
+        <v>3607</v>
       </c>
       <c r="E11" t="n">
         <v>162941</v>
@@ -13415,59 +13367,57 @@
         <v>170363</v>
       </c>
       <c r="U11" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="V11" t="n">
         <v>436471</v>
       </c>
       <c r="W11" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X11" t="b">
         <v>1</v>
       </c>
-      <c r="Y11"/>
-      <c r="Z11"/>
-      <c r="AA11" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="Y11" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z11" t="n">
         <v>0.264967834816922</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AA11" t="n">
         <v>0.0433255053181007</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>3587</v>
       </c>
       <c r="AD11" t="s">
         <v>19</v>
       </c>
       <c r="AE11" t="s">
-        <v>3590</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>3590</v>
-      </c>
-      <c r="AH11" t="n">
+        <v>3587</v>
+      </c>
+      <c r="AF11" t="n">
         <v>2</v>
       </c>
-      <c r="AI11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>3621</v>
+      <c r="AG11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>3618</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>3622</v>
+        <v>3619</v>
       </c>
       <c r="D12" t="s">
         <v>63</v>
@@ -13521,62 +13471,60 @@
         <v>162941</v>
       </c>
       <c r="U12" t="s">
-        <v>3623</v>
+        <v>3620</v>
       </c>
       <c r="V12" t="n">
         <v>322342</v>
       </c>
       <c r="W12" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X12" t="b">
         <v>1</v>
       </c>
-      <c r="Y12"/>
-      <c r="Z12"/>
-      <c r="AA12" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="Y12" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z12" t="n">
         <v>0.357998257285508</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AA12" t="n">
         <v>0.0584824622237757</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>3621</v>
       </c>
       <c r="AD12" t="s">
         <v>19</v>
       </c>
       <c r="AE12" t="s">
-        <v>3624</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>3624</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>3625</v>
+        <v>3621</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>3622</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>3626</v>
+        <v>3623</v>
       </c>
       <c r="D13" t="s">
-        <v>3588</v>
+        <v>3585</v>
       </c>
       <c r="E13" t="n">
         <v>162941</v>
@@ -13627,59 +13575,57 @@
         <v>173853</v>
       </c>
       <c r="U13" t="s">
-        <v>3617</v>
+        <v>3614</v>
       </c>
       <c r="V13" t="n">
         <v>113095</v>
       </c>
       <c r="W13" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X13" t="b">
         <v>1</v>
       </c>
-      <c r="Y13"/>
-      <c r="Z13"/>
-      <c r="AA13" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="Y13" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z13" t="n">
         <v>-0.829290425702044</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AA13" t="n">
         <v>0.172153585005738</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>3615</v>
       </c>
       <c r="AD13" t="s">
         <v>19</v>
       </c>
       <c r="AE13" t="s">
-        <v>3618</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>3618</v>
-      </c>
-      <c r="AH13" t="n">
+        <v>3615</v>
+      </c>
+      <c r="AF13" t="n">
         <v>4</v>
       </c>
-      <c r="AI13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>3627</v>
+      <c r="AG13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>3624</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>3628</v>
+        <v>3625</v>
       </c>
       <c r="D14" t="s">
         <v>63</v>
@@ -13733,59 +13679,57 @@
         <v>162941</v>
       </c>
       <c r="U14" t="s">
-        <v>3602</v>
+        <v>3599</v>
       </c>
       <c r="V14" t="n">
         <v>526335</v>
       </c>
       <c r="W14" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X14" t="b">
         <v>1</v>
       </c>
-      <c r="Y14"/>
-      <c r="Z14"/>
-      <c r="AA14" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="Y14" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z14" t="n">
         <v>0.20734254453402</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AA14" t="n">
         <v>0.0422930719892232</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>3600</v>
       </c>
       <c r="AD14" t="s">
         <v>19</v>
       </c>
       <c r="AE14" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>3629</v>
+        <v>3600</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>3626</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>3630</v>
+        <v>3627</v>
       </c>
       <c r="D15" t="s">
         <v>63</v>
@@ -13839,59 +13783,57 @@
         <v>162941</v>
       </c>
       <c r="U15" t="s">
-        <v>3631</v>
+        <v>3628</v>
       </c>
       <c r="V15" t="n">
         <v>113379</v>
       </c>
       <c r="W15" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X15" t="b">
         <v>1</v>
       </c>
-      <c r="Y15"/>
-      <c r="Z15"/>
-      <c r="AA15" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="Y15" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z15" t="n">
         <v>0.180020892843471</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AA15" t="n">
         <v>0.050796979673521</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>3629</v>
       </c>
       <c r="AD15" t="s">
         <v>19</v>
       </c>
       <c r="AE15" t="s">
-        <v>3632</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>3632</v>
-      </c>
-      <c r="AH15" t="n">
+        <v>3629</v>
+      </c>
+      <c r="AF15" t="n">
         <v>0</v>
       </c>
-      <c r="AI15" t="b">
+      <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AJ15" t="s">
-        <v>3633</v>
+      <c r="AH15" t="s">
+        <v>3630</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>3634</v>
+        <v>3631</v>
       </c>
       <c r="D16" t="s">
         <v>14</v>
@@ -13945,62 +13887,60 @@
         <v>164068</v>
       </c>
       <c r="U16" t="s">
-        <v>3606</v>
+        <v>3603</v>
       </c>
       <c r="V16" t="n">
         <v>742910</v>
       </c>
       <c r="W16" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X16" t="b">
         <v>1</v>
       </c>
-      <c r="Y16"/>
-      <c r="Z16"/>
-      <c r="AA16" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="Y16" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z16" t="n">
         <v>0.171887339696594</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AA16" t="n">
         <v>0.0481246732618178</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>3604</v>
       </c>
       <c r="AD16" t="s">
         <v>19</v>
       </c>
       <c r="AE16" t="s">
-        <v>3607</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>3607</v>
-      </c>
-      <c r="AH16" t="n">
+        <v>3604</v>
+      </c>
+      <c r="AF16" t="n">
         <v>0</v>
       </c>
-      <c r="AI16" t="b">
+      <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AJ16" t="s">
-        <v>3635</v>
+      <c r="AH16" t="s">
+        <v>3632</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>3636</v>
+        <v>3633</v>
       </c>
       <c r="D17" t="s">
-        <v>3637</v>
+        <v>3634</v>
       </c>
       <c r="E17" t="n">
         <v>161785</v>
@@ -14051,59 +13991,57 @@
         <v>167336</v>
       </c>
       <c r="U17" t="s">
-        <v>3623</v>
+        <v>3620</v>
       </c>
       <c r="V17" t="n">
         <v>205635</v>
       </c>
       <c r="W17" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X17" t="b">
         <v>1</v>
       </c>
-      <c r="Y17"/>
-      <c r="Z17"/>
-      <c r="AA17" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="Y17" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z17" t="n">
         <v>-0.173879436026059</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AA17" t="n">
         <v>0.127178200525584</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>3621</v>
       </c>
       <c r="AD17" t="s">
         <v>19</v>
       </c>
       <c r="AE17" t="s">
-        <v>3624</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>3624</v>
-      </c>
-      <c r="AH17" t="n">
+        <v>3621</v>
+      </c>
+      <c r="AF17" t="n">
         <v>3</v>
       </c>
-      <c r="AI17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>3636</v>
+      <c r="AG17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>3633</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>3638</v>
+        <v>3635</v>
       </c>
       <c r="D18" t="s">
         <v>63</v>
@@ -14157,59 +14095,57 @@
         <v>162941</v>
       </c>
       <c r="U18" t="s">
-        <v>3602</v>
+        <v>3599</v>
       </c>
       <c r="V18" t="n">
         <v>289692</v>
       </c>
       <c r="W18" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X18" t="b">
         <v>1</v>
       </c>
-      <c r="Y18"/>
-      <c r="Z18"/>
-      <c r="AA18" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="Y18" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z18" t="n">
         <v>-0.0740545591106971</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AA18" t="n">
         <v>0.0387303744423094</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>3600</v>
       </c>
       <c r="AD18" t="s">
         <v>19</v>
       </c>
       <c r="AE18" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>3603</v>
-      </c>
-      <c r="AH18" t="n">
+        <v>3600</v>
+      </c>
+      <c r="AF18" t="n">
         <v>2</v>
       </c>
-      <c r="AI18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>3639</v>
+      <c r="AG18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>3636</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B19" t="s">
         <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>3640</v>
+        <v>3637</v>
       </c>
       <c r="D19" t="s">
         <v>63</v>
@@ -14263,59 +14199,57 @@
         <v>162941</v>
       </c>
       <c r="U19" t="s">
-        <v>3641</v>
+        <v>3638</v>
       </c>
       <c r="V19" t="n">
         <v>130799</v>
       </c>
       <c r="W19" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X19" t="b">
         <v>1</v>
       </c>
-      <c r="Y19"/>
-      <c r="Z19"/>
-      <c r="AA19" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB19" t="n">
+      <c r="Y19" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z19" t="n">
         <v>-0.0747370124025052</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AA19" t="n">
         <v>0.0266460312425587</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>3639</v>
       </c>
       <c r="AD19" t="s">
         <v>19</v>
       </c>
       <c r="AE19" t="s">
-        <v>3642</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>3642</v>
-      </c>
-      <c r="AH19" t="n">
+        <v>3639</v>
+      </c>
+      <c r="AF19" t="n">
         <v>0</v>
       </c>
-      <c r="AI19" t="b">
+      <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AJ19" t="s">
-        <v>3643</v>
+      <c r="AH19" t="s">
+        <v>3640</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B20" t="s">
         <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>3644</v>
+        <v>3641</v>
       </c>
       <c r="D20" t="s">
         <v>63</v>
@@ -14369,59 +14303,57 @@
         <v>162941</v>
       </c>
       <c r="U20" t="s">
-        <v>3606</v>
+        <v>3603</v>
       </c>
       <c r="V20" t="n">
         <v>159473</v>
       </c>
       <c r="W20" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X20" t="b">
         <v>1</v>
       </c>
-      <c r="Y20"/>
-      <c r="Z20"/>
-      <c r="AA20" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="Y20" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z20" t="n">
         <v>0.0610772273039568</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AA20" t="n">
         <v>0.0218281695043658</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>3604</v>
       </c>
       <c r="AD20" t="s">
         <v>19</v>
       </c>
       <c r="AE20" t="s">
-        <v>3607</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>3607</v>
-      </c>
-      <c r="AH20" t="n">
+        <v>3604</v>
+      </c>
+      <c r="AF20" t="n">
         <v>0</v>
       </c>
-      <c r="AI20" t="b">
+      <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="s">
-        <v>3645</v>
+      <c r="AH20" t="s">
+        <v>3642</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B21" t="s">
         <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>3646</v>
+        <v>3643</v>
       </c>
       <c r="D21" t="s">
         <v>63</v>
@@ -14475,62 +14407,60 @@
         <v>162941</v>
       </c>
       <c r="U21" t="s">
-        <v>3606</v>
+        <v>3603</v>
       </c>
       <c r="V21" t="n">
         <v>505794</v>
       </c>
       <c r="W21" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X21" t="b">
         <v>1</v>
       </c>
-      <c r="Y21"/>
-      <c r="Z21"/>
-      <c r="AA21" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="Y21" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z21" t="n">
         <v>0.0355038226972509</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AA21" t="n">
         <v>0.0132146859903832</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>3604</v>
       </c>
       <c r="AD21" t="s">
         <v>19</v>
       </c>
       <c r="AE21" t="s">
-        <v>3607</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>3607</v>
-      </c>
-      <c r="AH21" t="n">
+        <v>3604</v>
+      </c>
+      <c r="AF21" t="n">
         <v>0</v>
       </c>
-      <c r="AI21" t="b">
+      <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AJ21" t="s">
-        <v>3647</v>
+      <c r="AH21" t="s">
+        <v>3644</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B22" t="s">
         <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>3648</v>
+        <v>3645</v>
       </c>
       <c r="D22" t="s">
-        <v>3649</v>
+        <v>3646</v>
       </c>
       <c r="E22" t="n">
         <v>161785</v>
@@ -14581,62 +14511,60 @@
         <v>176637</v>
       </c>
       <c r="U22" t="s">
-        <v>3606</v>
+        <v>3603</v>
       </c>
       <c r="V22" t="n">
         <v>231281</v>
       </c>
       <c r="W22" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X22" t="b">
         <v>1</v>
       </c>
-      <c r="Y22"/>
-      <c r="Z22"/>
-      <c r="AA22" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="Y22" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z22" t="n">
         <v>0.0578115561890814</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AA22" t="n">
         <v>0.0449836993988052</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>3604</v>
       </c>
       <c r="AD22" t="s">
         <v>19</v>
       </c>
       <c r="AE22" t="s">
-        <v>3607</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>3607</v>
-      </c>
-      <c r="AH22" t="n">
+        <v>3604</v>
+      </c>
+      <c r="AF22" t="n">
         <v>4</v>
       </c>
-      <c r="AI22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ22" t="s">
-        <v>3650</v>
+      <c r="AG22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>3647</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B23" t="s">
         <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>3651</v>
+        <v>3648</v>
       </c>
       <c r="D23" t="s">
-        <v>3652</v>
+        <v>3649</v>
       </c>
       <c r="E23" t="n">
         <v>135044</v>
@@ -14687,59 +14615,57 @@
         <v>154005</v>
       </c>
       <c r="U23" t="s">
-        <v>3613</v>
+        <v>3610</v>
       </c>
       <c r="V23" t="n">
         <v>600793</v>
       </c>
       <c r="W23" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X23" t="b">
         <v>1</v>
       </c>
-      <c r="Y23"/>
-      <c r="Z23"/>
-      <c r="AA23" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="Y23" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z23" t="n">
         <v>-0.165917349135744</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AA23" t="n">
         <v>0.0603163578819706</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>3611</v>
       </c>
       <c r="AD23" t="s">
         <v>19</v>
       </c>
       <c r="AE23" t="s">
-        <v>3614</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>3614</v>
-      </c>
-      <c r="AH23" t="n">
+        <v>3611</v>
+      </c>
+      <c r="AF23" t="n">
         <v>0</v>
       </c>
-      <c r="AI23" t="b">
+      <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AJ23" t="s">
-        <v>3653</v>
+      <c r="AH23" t="s">
+        <v>3650</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B24" t="s">
         <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>3654</v>
+        <v>3651</v>
       </c>
       <c r="D24" t="s">
         <v>63</v>
@@ -14793,62 +14719,60 @@
         <v>162941</v>
       </c>
       <c r="U24" t="s">
-        <v>3655</v>
+        <v>3652</v>
       </c>
       <c r="V24" t="n">
         <v>700594</v>
       </c>
       <c r="W24" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X24" t="b">
         <v>1</v>
       </c>
-      <c r="Y24"/>
-      <c r="Z24"/>
-      <c r="AA24" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="Y24" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z24" t="n">
         <v>0.0288291140858541</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AA24" t="n">
         <v>0.0125120845868916</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>3653</v>
       </c>
       <c r="AD24" t="s">
         <v>19</v>
       </c>
       <c r="AE24" t="s">
-        <v>3656</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>3656</v>
-      </c>
-      <c r="AH24" t="n">
+        <v>3653</v>
+      </c>
+      <c r="AF24" t="n">
         <v>2</v>
       </c>
-      <c r="AI24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ24" t="s">
-        <v>3657</v>
+      <c r="AG24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>3654</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B25" t="s">
         <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>3658</v>
+        <v>3655</v>
       </c>
       <c r="D25" t="s">
-        <v>3659</v>
+        <v>3656</v>
       </c>
       <c r="E25" t="n">
         <v>104931</v>
@@ -14899,62 +14823,60 @@
         <v>156275</v>
       </c>
       <c r="U25" t="s">
-        <v>3631</v>
+        <v>3628</v>
       </c>
       <c r="V25" t="n">
         <v>33054</v>
       </c>
       <c r="W25" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X25" t="b">
         <v>1</v>
       </c>
-      <c r="Y25"/>
-      <c r="Z25"/>
-      <c r="AA25" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB25" t="n">
+      <c r="Y25" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z25" t="n">
         <v>-0.0565135254594067</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AA25" t="n">
         <v>0.0297235901236087</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>3629</v>
       </c>
       <c r="AD25" t="s">
         <v>19</v>
       </c>
       <c r="AE25" t="s">
-        <v>3632</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG25" t="s">
-        <v>3632</v>
-      </c>
-      <c r="AH25" t="n">
+        <v>3629</v>
+      </c>
+      <c r="AF25" t="n">
         <v>2</v>
       </c>
-      <c r="AI25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ25" t="s">
-        <v>3660</v>
+      <c r="AG25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>3657</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B26" t="s">
         <v>15</v>
       </c>
       <c r="C26" t="s">
-        <v>3661</v>
+        <v>3658</v>
       </c>
       <c r="D26" t="s">
-        <v>3649</v>
+        <v>3646</v>
       </c>
       <c r="E26" t="n">
         <v>163645</v>
@@ -15005,62 +14927,60 @@
         <v>176637</v>
       </c>
       <c r="U26" t="s">
-        <v>3582</v>
+        <v>3579</v>
       </c>
       <c r="V26" t="n">
         <v>107256</v>
       </c>
       <c r="W26" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X26" t="b">
         <v>1</v>
       </c>
-      <c r="Y26"/>
-      <c r="Z26"/>
-      <c r="AA26" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB26" t="n">
+      <c r="Y26" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z26" t="n">
         <v>-0.0158961475744548</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AA26" t="n">
         <v>0.0306083356262737</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>3582</v>
       </c>
       <c r="AD26" t="s">
         <v>19</v>
       </c>
       <c r="AE26" t="s">
-        <v>3585</v>
-      </c>
-      <c r="AF26" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG26" t="s">
-        <v>3585</v>
-      </c>
-      <c r="AH26" t="n">
+        <v>3582</v>
+      </c>
+      <c r="AF26" t="n">
         <v>3</v>
       </c>
-      <c r="AI26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ26" t="s">
-        <v>3662</v>
+      <c r="AG26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>3659</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B27" t="s">
         <v>15</v>
       </c>
       <c r="C27" t="s">
-        <v>3663</v>
+        <v>3660</v>
       </c>
       <c r="D27" t="s">
-        <v>3652</v>
+        <v>3649</v>
       </c>
       <c r="E27" t="n">
         <v>108125</v>
@@ -15111,59 +15031,57 @@
         <v>154005</v>
       </c>
       <c r="U27" t="s">
-        <v>3641</v>
+        <v>3638</v>
       </c>
       <c r="V27" t="n">
         <v>139364</v>
       </c>
       <c r="W27" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X27" t="b">
         <v>1</v>
       </c>
-      <c r="Y27"/>
-      <c r="Z27"/>
-      <c r="AA27" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB27" t="n">
+      <c r="Y27" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z27" t="n">
         <v>-0.0843548745046768</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AA27" t="n">
         <v>0.0352475278689996</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>3639</v>
       </c>
       <c r="AD27" t="s">
         <v>19</v>
       </c>
       <c r="AE27" t="s">
-        <v>3642</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG27" t="s">
-        <v>3642</v>
-      </c>
-      <c r="AH27" t="n">
+        <v>3639</v>
+      </c>
+      <c r="AF27" t="n">
         <v>0</v>
       </c>
-      <c r="AI27" t="b">
+      <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AJ27" t="s">
-        <v>3664</v>
+      <c r="AH27" t="s">
+        <v>3661</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B28" t="s">
         <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>3665</v>
+        <v>3662</v>
       </c>
       <c r="D28" t="s">
         <v>63</v>
@@ -15217,59 +15135,57 @@
         <v>162941</v>
       </c>
       <c r="U28" t="s">
-        <v>3589</v>
+        <v>3586</v>
       </c>
       <c r="V28" t="n">
         <v>277617</v>
       </c>
       <c r="W28" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X28" t="b">
         <v>1</v>
       </c>
-      <c r="Y28"/>
-      <c r="Z28"/>
-      <c r="AA28" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB28" t="n">
+      <c r="Y28" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z28" t="n">
         <v>0.02734591510435</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AA28" t="n">
         <v>0.0126364056080832</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>3587</v>
       </c>
       <c r="AD28" t="s">
         <v>19</v>
       </c>
       <c r="AE28" t="s">
-        <v>3590</v>
-      </c>
-      <c r="AF28" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG28" t="s">
-        <v>3590</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ28" t="s">
-        <v>3666</v>
+        <v>3587</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH28" t="s">
+        <v>3663</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B29" t="s">
         <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>3667</v>
+        <v>3664</v>
       </c>
       <c r="D29" t="s">
         <v>63</v>
@@ -15323,62 +15239,60 @@
         <v>162941</v>
       </c>
       <c r="U29" t="s">
-        <v>3606</v>
+        <v>3603</v>
       </c>
       <c r="V29" t="n">
         <v>1041548</v>
       </c>
       <c r="W29" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X29" t="b">
         <v>1</v>
       </c>
-      <c r="Y29"/>
-      <c r="Z29"/>
-      <c r="AA29" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB29" t="n">
+      <c r="Y29" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z29" t="n">
         <v>-0.0344076013087804</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AA29" t="n">
         <v>0.0202359949170421</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>3604</v>
       </c>
       <c r="AD29" t="s">
         <v>19</v>
       </c>
       <c r="AE29" t="s">
-        <v>3607</v>
-      </c>
-      <c r="AF29" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG29" t="s">
-        <v>3607</v>
-      </c>
-      <c r="AH29" t="n">
+        <v>3604</v>
+      </c>
+      <c r="AF29" t="n">
         <v>2</v>
       </c>
-      <c r="AI29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ29" t="s">
-        <v>3668</v>
+      <c r="AG29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>3665</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B30" t="s">
         <v>15</v>
       </c>
       <c r="C30" t="s">
-        <v>3669</v>
+        <v>3666</v>
       </c>
       <c r="D30" t="s">
-        <v>3588</v>
+        <v>3585</v>
       </c>
       <c r="E30" t="n">
         <v>161785</v>
@@ -15429,59 +15343,57 @@
         <v>173853</v>
       </c>
       <c r="U30" t="s">
-        <v>3670</v>
+        <v>3667</v>
       </c>
       <c r="V30" t="n">
         <v>409169</v>
       </c>
       <c r="W30" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X30" t="b">
         <v>1</v>
       </c>
-      <c r="Y30"/>
-      <c r="Z30"/>
-      <c r="AA30" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB30" t="n">
+      <c r="Y30" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z30" t="n">
         <v>0.147849289830142</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AA30" t="n">
         <v>0.0594309016595541</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>3668</v>
       </c>
       <c r="AD30" t="s">
         <v>19</v>
       </c>
       <c r="AE30" t="s">
-        <v>3671</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG30" t="s">
-        <v>3671</v>
-      </c>
-      <c r="AH30" t="n">
+        <v>3668</v>
+      </c>
+      <c r="AF30" t="n">
         <v>0</v>
       </c>
-      <c r="AI30" t="b">
+      <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AJ30" t="s">
-        <v>3672</v>
+      <c r="AH30" t="s">
+        <v>3669</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>3580</v>
+        <v>3577</v>
       </c>
       <c r="B31" t="s">
         <v>15</v>
       </c>
       <c r="C31" t="s">
-        <v>3673</v>
+        <v>3670</v>
       </c>
       <c r="D31" t="s">
         <v>63</v>
@@ -15535,48 +15447,46 @@
         <v>162941</v>
       </c>
       <c r="U31" t="s">
-        <v>3613</v>
+        <v>3610</v>
       </c>
       <c r="V31" t="n">
         <v>1162792</v>
       </c>
       <c r="W31" t="s">
-        <v>3583</v>
+        <v>3580</v>
       </c>
       <c r="X31" t="b">
         <v>1</v>
       </c>
-      <c r="Y31"/>
-      <c r="Z31"/>
-      <c r="AA31" t="s">
-        <v>3584</v>
-      </c>
-      <c r="AB31" t="n">
+      <c r="Y31" t="s">
+        <v>3581</v>
+      </c>
+      <c r="Z31" t="n">
         <v>-0.0921020950848088</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AA31" t="n">
         <v>0.0361924586372988</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>3611</v>
       </c>
       <c r="AD31" t="s">
         <v>19</v>
       </c>
       <c r="AE31" t="s">
-        <v>3614</v>
-      </c>
-      <c r="AF31" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG31" t="s">
-        <v>3614</v>
-      </c>
-      <c r="AH31" t="n">
+        <v>3611</v>
+      </c>
+      <c r="AF31" t="n">
         <v>0</v>
       </c>
-      <c r="AI31" t="b">
+      <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AJ31" t="s">
-        <v>3674</v>
+      <c r="AH31" t="s">
+        <v>3671</v>
       </c>
     </row>
   </sheetData>
@@ -15655,37 +15565,28 @@
         <v>3566</v>
       </c>
       <c r="V1" t="s">
-        <v>3675</v>
+        <v>41</v>
       </c>
       <c r="W1" t="s">
-        <v>3676</v>
+        <v>3570</v>
       </c>
       <c r="X1" t="s">
-        <v>3677</v>
+        <v>3571</v>
       </c>
       <c r="Y1" t="s">
-        <v>3678</v>
+        <v>3572</v>
       </c>
       <c r="Z1" t="s">
-        <v>3679</v>
+        <v>12</v>
       </c>
       <c r="AA1" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
       <c r="AB1" t="s">
-        <v>3575</v>
+        <v>3672</v>
       </c>
       <c r="AC1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD1" t="s">
         <v>3576</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>3680</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>3579</v>
       </c>
     </row>
     <row r="2">
@@ -15693,7 +15594,7 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>3681</v>
+        <v>3673</v>
       </c>
       <c r="C2" t="s">
         <v>63</v>
@@ -15753,37 +15654,28 @@
         <v>162825</v>
       </c>
       <c r="V2" t="n">
-        <v>20.6900420073926</v>
+        <v>0.660787728481922</v>
       </c>
       <c r="W2" t="n">
-        <v>7.25579110416833</v>
-      </c>
-      <c r="X2" t="n">
-        <v>3.94590829381122</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.75129073472609</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>7.2206991361486</v>
+        <v>0.0616402524031109</v>
+      </c>
+      <c r="X2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>19</v>
       </c>
       <c r="AA2" t="s">
         <v>19</v>
       </c>
-      <c r="AB2" t="s">
-        <v>19</v>
+      <c r="AB2" t="n">
+        <v>0</v>
       </c>
       <c r="AC2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>3682</v>
+        <v>3674</v>
       </c>
     </row>
     <row r="3">
@@ -15791,10 +15683,10 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>3683</v>
+        <v>3675</v>
       </c>
       <c r="C3" t="s">
-        <v>3684</v>
+        <v>3676</v>
       </c>
       <c r="D3" t="n">
         <v>201163</v>
@@ -15851,37 +15743,28 @@
         <v>209811</v>
       </c>
       <c r="V3" t="n">
-        <v>10.0179801644615</v>
+        <v>0.376038838562136</v>
       </c>
       <c r="W3" t="n">
-        <v>5.38570545101514</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4.14027313685419</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>5.01816043449022</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>5.53372547370778</v>
+        <v>0.0562495395691637</v>
+      </c>
+      <c r="X3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>19</v>
       </c>
       <c r="AA3" t="s">
         <v>19</v>
       </c>
-      <c r="AB3" t="s">
-        <v>19</v>
+      <c r="AB3" t="n">
+        <v>0</v>
       </c>
       <c r="AC3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>3685</v>
+        <v>3677</v>
       </c>
     </row>
     <row r="4">
@@ -15889,10 +15772,10 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>3686</v>
+        <v>3678</v>
       </c>
       <c r="C4" t="s">
-        <v>3684</v>
+        <v>3676</v>
       </c>
       <c r="D4" t="n">
         <v>201163</v>
@@ -15949,37 +15832,28 @@
         <v>201054</v>
       </c>
       <c r="V4" t="n">
-        <v>9.98092009940717</v>
+        <v>0.497191073318116</v>
       </c>
       <c r="W4" t="n">
-        <v>4.83077282622474</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.42357561703096</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.03130453941153</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.51832919930148</v>
+        <v>0.0898813374690677</v>
+      </c>
+      <c r="X4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>19</v>
       </c>
       <c r="AA4" t="s">
         <v>19</v>
       </c>
-      <c r="AB4" t="s">
-        <v>19</v>
+      <c r="AB4" t="n">
+        <v>0</v>
       </c>
       <c r="AC4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>3687</v>
+        <v>3679</v>
       </c>
     </row>
     <row r="5">
@@ -15987,10 +15861,10 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>3688</v>
+        <v>3680</v>
       </c>
       <c r="C5" t="s">
-        <v>3689</v>
+        <v>3681</v>
       </c>
       <c r="D5" t="n">
         <v>155078</v>
@@ -16047,37 +15921,28 @@
         <v>153892</v>
       </c>
       <c r="V5" t="n">
-        <v>4.51581189451102</v>
+        <v>0.3729872187608</v>
       </c>
       <c r="W5" t="n">
-        <v>2.50269662004464</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.48918677517638</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>5.72434977386621</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5.43582989237115</v>
+        <v>0.0849554075733703</v>
+      </c>
+      <c r="X5" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>19</v>
       </c>
       <c r="AA5" t="s">
         <v>19</v>
       </c>
-      <c r="AB5" t="s">
-        <v>19</v>
+      <c r="AB5" t="n">
+        <v>0</v>
       </c>
       <c r="AC5" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>3690</v>
+        <v>3682</v>
       </c>
     </row>
     <row r="6">
@@ -16085,10 +15950,10 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>3691</v>
+        <v>3683</v>
       </c>
       <c r="C6" t="s">
-        <v>3684</v>
+        <v>3676</v>
       </c>
       <c r="D6" t="n">
         <v>201163</v>
@@ -16145,37 +16010,28 @@
         <v>206141</v>
       </c>
       <c r="V6" t="n">
-        <v>7.17236647844655</v>
+        <v>0.220950782651039</v>
       </c>
       <c r="W6" t="n">
-        <v>3.00044221831839</v>
-      </c>
-      <c r="X6" t="n">
-        <v>4.15473715631131</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.57495484961813</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5.42267724417236</v>
+        <v>0.0469356969667421</v>
+      </c>
+      <c r="X6" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>19</v>
       </c>
       <c r="AA6" t="s">
         <v>19</v>
       </c>
-      <c r="AB6" t="s">
-        <v>19</v>
+      <c r="AB6" t="n">
+        <v>0</v>
       </c>
       <c r="AC6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>3691</v>
+        <v>3683</v>
       </c>
     </row>
     <row r="7">
@@ -16183,10 +16039,10 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>3692</v>
+        <v>3684</v>
       </c>
       <c r="C7" t="s">
-        <v>3588</v>
+        <v>3585</v>
       </c>
       <c r="D7" t="n">
         <v>173853</v>
@@ -16243,37 +16099,28 @@
         <v>173706</v>
       </c>
       <c r="V7" t="n">
-        <v>6.02093285100529</v>
+        <v>0.353507950012734</v>
       </c>
       <c r="W7" t="n">
-        <v>3.11930976557231</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.29494606045689</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.80064178741395</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.3471776470844</v>
+        <v>0.097898469664252</v>
+      </c>
+      <c r="X7" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>19</v>
       </c>
       <c r="AA7" t="s">
         <v>19</v>
       </c>
-      <c r="AB7" t="s">
-        <v>19</v>
+      <c r="AB7" t="n">
+        <v>0</v>
       </c>
       <c r="AC7" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>3693</v>
+        <v>3685</v>
       </c>
     </row>
     <row r="8">
@@ -16281,10 +16128,10 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>3694</v>
+        <v>3686</v>
       </c>
       <c r="C8" t="s">
-        <v>3684</v>
+        <v>3676</v>
       </c>
       <c r="D8" t="n">
         <v>201163</v>
@@ -16341,37 +16188,28 @@
         <v>224279</v>
       </c>
       <c r="V8" t="n">
-        <v>-4.44737834713673</v>
+        <v>-0.391120757950955</v>
       </c>
       <c r="W8" t="n">
-        <v>-3.037006902413</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-3.81695912225005</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-3.05037197007126</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-2.79332587970821</v>
+        <v>0.110404171405559</v>
+      </c>
+      <c r="X8" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>19</v>
       </c>
       <c r="AA8" t="s">
         <v>19</v>
       </c>
-      <c r="AB8" t="s">
-        <v>19</v>
+      <c r="AB8" t="n">
+        <v>0</v>
       </c>
       <c r="AC8" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>3695</v>
+        <v>3687</v>
       </c>
     </row>
     <row r="9">
@@ -16379,7 +16217,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>3696</v>
+        <v>3688</v>
       </c>
       <c r="C9" t="s">
         <v>63</v>
@@ -16439,37 +16277,28 @@
         <v>199426</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.25783809231649</v>
+        <v>-0.392944173208407</v>
       </c>
       <c r="W9" t="n">
-        <v>-4.08612865793978</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-3.710144548979</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>-2.8957653932068</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-4.14114209722375</v>
+        <v>0.120257841701613</v>
+      </c>
+      <c r="X9" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>19</v>
       </c>
       <c r="AA9" t="s">
         <v>19</v>
       </c>
-      <c r="AB9" t="s">
-        <v>19</v>
+      <c r="AB9" t="n">
+        <v>0</v>
       </c>
       <c r="AC9" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>3697</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="10">
@@ -16477,10 +16306,10 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>3698</v>
+        <v>3690</v>
       </c>
       <c r="C10" t="s">
-        <v>3699</v>
+        <v>3691</v>
       </c>
       <c r="D10" t="n">
         <v>161785</v>
@@ -16537,37 +16366,28 @@
         <v>158305</v>
       </c>
       <c r="V10" t="n">
-        <v>4.98874929192682</v>
+        <v>0.287528100278048</v>
       </c>
       <c r="W10" t="n">
-        <v>0.894645485270741</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.934027203114927</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.59643428061117</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.81146042063519</v>
+        <v>0.112170783545896</v>
+      </c>
+      <c r="X10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>19</v>
       </c>
       <c r="AA10" t="s">
         <v>19</v>
       </c>
-      <c r="AB10" t="s">
-        <v>19</v>
+      <c r="AB10" t="n">
+        <v>0.000609756097560976</v>
       </c>
       <c r="AC10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0.000609756097560976</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>3698</v>
+        <v>3690</v>
       </c>
     </row>
     <row r="11">
@@ -16575,10 +16395,10 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>3700</v>
+        <v>3692</v>
       </c>
       <c r="C11" t="s">
-        <v>3649</v>
+        <v>3646</v>
       </c>
       <c r="D11" t="n">
         <v>154005</v>
@@ -16635,37 +16455,28 @@
         <v>186369</v>
       </c>
       <c r="V11" t="n">
-        <v>4.63048729898059</v>
+        <v>0.175662148197296</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.350162389602722</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-0.726208616612339</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.318145243281335</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.81344506246431</v>
+        <v>0.0962146883382891</v>
+      </c>
+      <c r="X11" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>19</v>
       </c>
       <c r="AA11" t="s">
         <v>19</v>
       </c>
-      <c r="AB11" t="s">
-        <v>19</v>
+      <c r="AB11" t="n">
+        <v>0.00082135523613963</v>
       </c>
       <c r="AC11" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0.00082135523613963</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>3701</v>
+        <v>3693</v>
       </c>
     </row>
     <row r="12">
@@ -16673,10 +16484,10 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>3702</v>
+        <v>3694</v>
       </c>
       <c r="C12" t="s">
-        <v>3684</v>
+        <v>3676</v>
       </c>
       <c r="D12" t="n">
         <v>201163</v>
@@ -16733,37 +16544,28 @@
         <v>177365</v>
       </c>
       <c r="V12" t="n">
-        <v>4.93262718667617</v>
+        <v>0.026117915231625</v>
       </c>
       <c r="W12" t="n">
-        <v>1.8260848216344</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.702814554234693</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.41622230320658</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0.287461864069011</v>
+        <v>0.0110310016429418</v>
+      </c>
+      <c r="X12" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>19</v>
       </c>
       <c r="AA12" t="s">
         <v>19</v>
       </c>
-      <c r="AB12" t="s">
-        <v>19</v>
+      <c r="AB12" t="n">
+        <v>0.00082135523613963</v>
       </c>
       <c r="AC12" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0.00082135523613963</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>3703</v>
+        <v>3695</v>
       </c>
     </row>
     <row r="13">
@@ -16771,10 +16573,10 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>3704</v>
+        <v>3696</v>
       </c>
       <c r="C13" t="s">
-        <v>3652</v>
+        <v>3649</v>
       </c>
       <c r="D13" t="n">
         <v>106134</v>
@@ -16831,37 +16633,28 @@
         <v>152717</v>
       </c>
       <c r="V13" t="n">
-        <v>4.1817612221337</v>
+        <v>0.346842530879398</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13426553407699</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.61941277163533</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.646885520732201</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.56005541819611</v>
+        <v>0.147705608351039</v>
+      </c>
+      <c r="X13" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>19</v>
       </c>
       <c r="AA13" t="s">
         <v>19</v>
       </c>
-      <c r="AB13" t="s">
-        <v>19</v>
+      <c r="AB13" t="n">
+        <v>0.00082135523613963</v>
       </c>
       <c r="AC13" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0.00082135523613963</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>3705</v>
+        <v>3697</v>
       </c>
     </row>
     <row r="14">
@@ -16869,10 +16662,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>3706</v>
+        <v>3698</v>
       </c>
       <c r="C14" t="s">
-        <v>3649</v>
+        <v>3646</v>
       </c>
       <c r="D14" t="n">
         <v>154005</v>
@@ -16929,37 +16722,28 @@
         <v>130625</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.13517379522798</v>
+        <v>-0.0843472617297379</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.04832350350934</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-3.55648518321774</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>-3.10087617776552</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>-0.00643438209025401</v>
+        <v>0.0532217417800743</v>
+      </c>
+      <c r="X14" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>19</v>
       </c>
       <c r="AA14" t="s">
         <v>19</v>
       </c>
-      <c r="AB14" t="s">
-        <v>19</v>
+      <c r="AB14" t="n">
+        <v>0.00287514582086403</v>
       </c>
       <c r="AC14" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0.00287514582086403</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>3707</v>
+        <v>3699</v>
       </c>
     </row>
     <row r="15">
@@ -16967,7 +16751,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>3708</v>
+        <v>3700</v>
       </c>
       <c r="C15" t="s">
         <v>63</v>
@@ -17027,37 +16811,28 @@
         <v>162479</v>
       </c>
       <c r="V15" t="n">
-        <v>4.41707090568263</v>
+        <v>0.0457951523270885</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.442160706637</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0.83961963173824</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.7558201441076</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0.530356739821017</v>
+        <v>0.0240817214177138</v>
+      </c>
+      <c r="X15" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>19</v>
       </c>
       <c r="AA15" t="s">
         <v>19</v>
       </c>
-      <c r="AB15" t="s">
-        <v>19</v>
+      <c r="AB15" t="n">
+        <v>0.00301204819277108</v>
       </c>
       <c r="AC15" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0.00301204819277108</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>3708</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="16">
@@ -17065,10 +16840,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>3709</v>
+        <v>3701</v>
       </c>
       <c r="C16" t="s">
-        <v>3710</v>
+        <v>3702</v>
       </c>
       <c r="D16" t="n">
         <v>154005</v>
@@ -17125,37 +16900,28 @@
         <v>119413</v>
       </c>
       <c r="V16" t="n">
-        <v>-3.67716915198294</v>
+        <v>-0.0518449600127349</v>
       </c>
       <c r="W16" t="n">
-        <v>1.54972947902402</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-0.900130054788705</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.502745190500745</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>-2.06210973724229</v>
+        <v>0.0376157012304118</v>
+      </c>
+      <c r="X16" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>19</v>
       </c>
       <c r="AA16" t="s">
         <v>19</v>
       </c>
-      <c r="AB16" t="s">
-        <v>19</v>
+      <c r="AB16" t="n">
+        <v>0.00645994832041344</v>
       </c>
       <c r="AC16" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0.00645994832041344</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>3711</v>
+        <v>3703</v>
       </c>
     </row>
     <row r="17">
@@ -17163,10 +16929,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>3712</v>
+        <v>3704</v>
       </c>
       <c r="C17" t="s">
-        <v>3713</v>
+        <v>3705</v>
       </c>
       <c r="D17" t="n">
         <v>201163</v>
@@ -17223,37 +16989,28 @@
         <v>227975</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.60357502326634</v>
+        <v>-0.519085763167932</v>
       </c>
       <c r="W17" t="n">
-        <v>-1.25331351882528</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-2.08293958088746</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>-2.56657940525935</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0.282180249952058</v>
+        <v>0.314146497304582</v>
+      </c>
+      <c r="X17" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>19</v>
       </c>
       <c r="AA17" t="s">
         <v>19</v>
       </c>
-      <c r="AB17" t="s">
-        <v>19</v>
+      <c r="AB17" t="n">
+        <v>0.011691418645286</v>
       </c>
       <c r="AC17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0.011691418645286</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>3712</v>
+        <v>3704</v>
       </c>
     </row>
     <row r="18">
@@ -17261,10 +17018,10 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>3714</v>
+        <v>3706</v>
       </c>
       <c r="C18" t="s">
-        <v>3713</v>
+        <v>3705</v>
       </c>
       <c r="D18" t="n">
         <v>201163</v>
@@ -17321,37 +17078,28 @@
         <v>210573</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.706094512961</v>
+        <v>-0.0941196908291531</v>
       </c>
       <c r="W18" t="n">
-        <v>-1.40919694393126</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-2.35147759811356</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>-1.79232312035126</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>-0.134680539624163</v>
+        <v>0.0517598037000968</v>
+      </c>
+      <c r="X18" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>19</v>
       </c>
       <c r="AA18" t="s">
         <v>19</v>
       </c>
-      <c r="AB18" t="s">
-        <v>19</v>
+      <c r="AB18" t="n">
+        <v>0.0193756727664155</v>
       </c>
       <c r="AC18" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0.0193756727664155</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>3715</v>
+        <v>3707</v>
       </c>
     </row>
     <row r="19">
@@ -17359,10 +17107,10 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>3716</v>
+        <v>3708</v>
       </c>
       <c r="C19" t="s">
-        <v>3684</v>
+        <v>3676</v>
       </c>
       <c r="D19" t="n">
         <v>4184</v>
@@ -17419,37 +17167,28 @@
         <v>242468</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.35777676587879</v>
+        <v>-0.155471328788283</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.360031065113524</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-1.60858197834854</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>-3.18667349113555</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0.504012559689741</v>
+        <v>0.136807534960099</v>
+      </c>
+      <c r="X19" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>19</v>
       </c>
       <c r="AA19" t="s">
         <v>19</v>
       </c>
-      <c r="AB19" t="s">
-        <v>19</v>
+      <c r="AB19" t="n">
+        <v>0.0464551700022927</v>
       </c>
       <c r="AC19" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0.0464551700022927</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>3717</v>
+        <v>3709</v>
       </c>
     </row>
   </sheetData>
@@ -17480,34 +17219,34 @@
         <v>28</v>
       </c>
       <c r="F1" t="s">
-        <v>3718</v>
+        <v>3710</v>
       </c>
       <c r="G1" t="s">
         <v>2085</v>
       </c>
       <c r="H1" t="s">
-        <v>3719</v>
+        <v>3711</v>
       </c>
       <c r="I1" t="s">
-        <v>3720</v>
+        <v>3712</v>
       </c>
       <c r="J1" t="s">
         <v>2130</v>
       </c>
       <c r="K1" t="s">
-        <v>3721</v>
+        <v>3713</v>
       </c>
       <c r="L1" t="s">
-        <v>3722</v>
+        <v>3714</v>
       </c>
       <c r="M1" t="s">
-        <v>3723</v>
+        <v>3715</v>
       </c>
       <c r="N1" t="s">
-        <v>3724</v>
+        <v>3716</v>
       </c>
       <c r="O1" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="P1" t="s">
         <v>3566</v>
@@ -17527,33 +17266,33 @@
         <v>771</v>
       </c>
       <c r="E2" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F2" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G2" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H2"/>
       <c r="I2"/>
       <c r="J2" t="s">
-        <v>3728</v>
+        <v>3720</v>
       </c>
       <c r="K2" t="s">
-        <v>3729</v>
+        <v>3721</v>
       </c>
       <c r="L2" t="s">
-        <v>3728</v>
+        <v>3720</v>
       </c>
       <c r="M2" t="s">
-        <v>3730</v>
+        <v>3722</v>
       </c>
       <c r="N2" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O2" t="s">
-        <v>3732</v>
+        <v>3724</v>
       </c>
       <c r="P2" t="n">
         <v>108406</v>
@@ -17573,33 +17312,33 @@
         <v>1566</v>
       </c>
       <c r="E3" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F3" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G3" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
       <c r="J3" t="s">
-        <v>3733</v>
+        <v>3725</v>
       </c>
       <c r="K3" t="s">
-        <v>3734</v>
+        <v>3726</v>
       </c>
       <c r="L3" t="s">
-        <v>3733</v>
+        <v>3725</v>
       </c>
       <c r="M3" t="s">
-        <v>3735</v>
+        <v>3727</v>
       </c>
       <c r="N3" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O3" t="s">
-        <v>3736</v>
+        <v>3728</v>
       </c>
       <c r="P3" t="n">
         <v>109888</v>
@@ -17619,30 +17358,30 @@
         <v>868</v>
       </c>
       <c r="E4" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F4" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G4" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4" t="s">
-        <v>3738</v>
+        <v>3730</v>
       </c>
       <c r="K4" t="s">
-        <v>3739</v>
+        <v>3731</v>
       </c>
       <c r="L4" t="s">
-        <v>3738</v>
+        <v>3730</v>
       </c>
       <c r="M4" t="s">
-        <v>3740</v>
+        <v>3732</v>
       </c>
       <c r="N4" t="s">
-        <v>3741</v>
+        <v>3733</v>
       </c>
       <c r="O4"/>
       <c r="P4" t="n">
@@ -17663,33 +17402,33 @@
         <v>567</v>
       </c>
       <c r="E5" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F5" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G5" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5" t="s">
-        <v>3742</v>
+        <v>3734</v>
       </c>
       <c r="K5" t="s">
-        <v>3743</v>
+        <v>3735</v>
       </c>
       <c r="L5" t="s">
-        <v>3742</v>
+        <v>3734</v>
       </c>
       <c r="M5" t="s">
-        <v>3744</v>
+        <v>3736</v>
       </c>
       <c r="N5" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O5" t="s">
-        <v>3745</v>
+        <v>3737</v>
       </c>
       <c r="P5" t="n">
         <v>112199</v>
@@ -17709,30 +17448,30 @@
         <v>462</v>
       </c>
       <c r="E6" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F6" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G6" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
       <c r="J6" t="s">
-        <v>3746</v>
+        <v>3738</v>
       </c>
       <c r="K6" t="s">
-        <v>3747</v>
+        <v>3739</v>
       </c>
       <c r="L6" t="s">
-        <v>3746</v>
+        <v>3738</v>
       </c>
       <c r="M6" t="s">
-        <v>3740</v>
+        <v>3732</v>
       </c>
       <c r="N6" t="s">
-        <v>3741</v>
+        <v>3733</v>
       </c>
       <c r="O6"/>
       <c r="P6" t="n">
@@ -17753,30 +17492,30 @@
         <v>255</v>
       </c>
       <c r="E7" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F7" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G7" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
       <c r="J7" t="s">
-        <v>3748</v>
+        <v>3740</v>
       </c>
       <c r="K7" t="s">
-        <v>3749</v>
+        <v>3741</v>
       </c>
       <c r="L7" t="s">
-        <v>3748</v>
+        <v>3740</v>
       </c>
       <c r="M7" t="s">
-        <v>3740</v>
+        <v>3732</v>
       </c>
       <c r="N7" t="s">
-        <v>3741</v>
+        <v>3733</v>
       </c>
       <c r="O7"/>
       <c r="P7" t="n">
@@ -17797,30 +17536,30 @@
         <v>315</v>
       </c>
       <c r="E8" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F8" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G8" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H8"/>
       <c r="I8"/>
       <c r="J8" t="s">
-        <v>3750</v>
+        <v>3742</v>
       </c>
       <c r="K8" t="s">
-        <v>3751</v>
+        <v>3743</v>
       </c>
       <c r="L8" t="s">
-        <v>3750</v>
+        <v>3742</v>
       </c>
       <c r="M8" t="s">
-        <v>3740</v>
+        <v>3732</v>
       </c>
       <c r="N8" t="s">
-        <v>3741</v>
+        <v>3733</v>
       </c>
       <c r="O8"/>
       <c r="P8" t="n">
@@ -17841,33 +17580,33 @@
         <v>969</v>
       </c>
       <c r="E9" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F9" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G9" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H9"/>
       <c r="I9"/>
       <c r="J9" t="s">
-        <v>3752</v>
+        <v>3744</v>
       </c>
       <c r="K9" t="s">
-        <v>3753</v>
+        <v>3745</v>
       </c>
       <c r="L9" t="s">
-        <v>3752</v>
+        <v>3744</v>
       </c>
       <c r="M9" t="s">
-        <v>3754</v>
+        <v>3746</v>
       </c>
       <c r="N9" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O9" t="s">
-        <v>3755</v>
+        <v>3747</v>
       </c>
       <c r="P9" t="n">
         <v>117864</v>
@@ -17887,33 +17626,33 @@
         <v>552</v>
       </c>
       <c r="E10" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F10" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G10" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H10"/>
       <c r="I10"/>
       <c r="J10" t="s">
-        <v>3756</v>
+        <v>3748</v>
       </c>
       <c r="K10" t="s">
-        <v>3757</v>
+        <v>3749</v>
       </c>
       <c r="L10" t="s">
-        <v>3756</v>
+        <v>3748</v>
       </c>
       <c r="M10" t="s">
-        <v>3758</v>
+        <v>3750</v>
       </c>
       <c r="N10" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O10" t="s">
-        <v>3759</v>
+        <v>3751</v>
       </c>
       <c r="P10" t="n">
         <v>118896</v>
@@ -17933,33 +17672,33 @@
         <v>744</v>
       </c>
       <c r="E11" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F11" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G11" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H11"/>
       <c r="I11"/>
       <c r="J11" t="s">
-        <v>3709</v>
+        <v>3701</v>
       </c>
       <c r="K11" t="s">
-        <v>3760</v>
+        <v>3752</v>
       </c>
       <c r="L11" t="s">
-        <v>3709</v>
+        <v>3701</v>
       </c>
       <c r="M11" t="s">
-        <v>3761</v>
+        <v>3753</v>
       </c>
       <c r="N11" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O11" t="s">
-        <v>3711</v>
+        <v>3703</v>
       </c>
       <c r="P11" t="n">
         <v>119946</v>
@@ -17979,33 +17718,33 @@
         <v>1383</v>
       </c>
       <c r="E12" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F12" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G12" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H12"/>
       <c r="I12"/>
       <c r="J12" t="s">
-        <v>3762</v>
+        <v>3754</v>
       </c>
       <c r="K12" t="s">
-        <v>3763</v>
+        <v>3755</v>
       </c>
       <c r="L12" t="s">
-        <v>3762</v>
+        <v>3754</v>
       </c>
       <c r="M12" t="s">
-        <v>3764</v>
+        <v>3756</v>
       </c>
       <c r="N12" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O12" t="s">
-        <v>3765</v>
+        <v>3757</v>
       </c>
       <c r="P12" t="n">
         <v>121637</v>
@@ -18025,30 +17764,30 @@
         <v>474</v>
       </c>
       <c r="E13" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F13" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G13" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H13"/>
       <c r="I13"/>
       <c r="J13" t="s">
-        <v>3766</v>
+        <v>3758</v>
       </c>
       <c r="K13" t="s">
-        <v>3767</v>
+        <v>3759</v>
       </c>
       <c r="L13" t="s">
-        <v>3766</v>
+        <v>3758</v>
       </c>
       <c r="M13" t="s">
-        <v>3740</v>
+        <v>3732</v>
       </c>
       <c r="N13" t="s">
-        <v>3741</v>
+        <v>3733</v>
       </c>
       <c r="O13"/>
       <c r="P13" t="n">
@@ -18069,30 +17808,30 @@
         <v>720</v>
       </c>
       <c r="E14" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F14" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G14" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H14"/>
       <c r="I14"/>
       <c r="J14" t="s">
-        <v>3768</v>
+        <v>3760</v>
       </c>
       <c r="K14" t="s">
-        <v>3769</v>
+        <v>3761</v>
       </c>
       <c r="L14" t="s">
-        <v>3768</v>
+        <v>3760</v>
       </c>
       <c r="M14" t="s">
-        <v>3770</v>
+        <v>3762</v>
       </c>
       <c r="N14" t="s">
-        <v>3741</v>
+        <v>3733</v>
       </c>
       <c r="O14"/>
       <c r="P14" t="n">
@@ -18113,33 +17852,33 @@
         <v>1812</v>
       </c>
       <c r="E15" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F15" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G15" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H15"/>
       <c r="I15"/>
       <c r="J15" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="K15" t="s">
-        <v>3772</v>
+        <v>3764</v>
       </c>
       <c r="L15" t="s">
-        <v>3771</v>
+        <v>3763</v>
       </c>
       <c r="M15" t="s">
-        <v>3773</v>
+        <v>3765</v>
       </c>
       <c r="N15" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O15" t="s">
-        <v>3774</v>
+        <v>3766</v>
       </c>
       <c r="P15" t="n">
         <v>129376</v>
@@ -18159,33 +17898,33 @@
         <v>798</v>
       </c>
       <c r="E16" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F16" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G16" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16" t="s">
-        <v>3706</v>
+        <v>3698</v>
       </c>
       <c r="K16" t="s">
-        <v>3775</v>
+        <v>3767</v>
       </c>
       <c r="L16" t="s">
-        <v>3706</v>
+        <v>3698</v>
       </c>
       <c r="M16" t="s">
-        <v>3776</v>
+        <v>3768</v>
       </c>
       <c r="N16" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O16" t="s">
-        <v>3707</v>
+        <v>3699</v>
       </c>
       <c r="P16" t="n">
         <v>131144</v>
@@ -18205,33 +17944,33 @@
         <v>852</v>
       </c>
       <c r="E17" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F17" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G17" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="K17" t="s">
-        <v>3778</v>
+        <v>3770</v>
       </c>
       <c r="L17" t="s">
-        <v>3777</v>
+        <v>3769</v>
       </c>
       <c r="M17" t="s">
-        <v>3779</v>
+        <v>3771</v>
       </c>
       <c r="N17" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O17" t="s">
-        <v>3780</v>
+        <v>3772</v>
       </c>
       <c r="P17" t="n">
         <v>132698</v>
@@ -18251,33 +17990,33 @@
         <v>3150</v>
       </c>
       <c r="E18" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F18" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G18" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H18"/>
       <c r="I18"/>
       <c r="J18" t="s">
-        <v>3781</v>
+        <v>3773</v>
       </c>
       <c r="K18" t="s">
-        <v>3782</v>
+        <v>3774</v>
       </c>
       <c r="L18" t="s">
-        <v>3781</v>
+        <v>3773</v>
       </c>
       <c r="M18" t="s">
-        <v>3783</v>
+        <v>3775</v>
       </c>
       <c r="N18" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O18" t="s">
-        <v>3784</v>
+        <v>3776</v>
       </c>
       <c r="P18" t="n">
         <v>135298</v>
@@ -18297,33 +18036,33 @@
         <v>1251</v>
       </c>
       <c r="E19" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F19" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G19" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="K19" t="s">
-        <v>3786</v>
+        <v>3778</v>
       </c>
       <c r="L19" t="s">
-        <v>3785</v>
+        <v>3777</v>
       </c>
       <c r="M19" t="s">
-        <v>3787</v>
+        <v>3779</v>
       </c>
       <c r="N19" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O19" t="s">
-        <v>3788</v>
+        <v>3780</v>
       </c>
       <c r="P19" t="n">
         <v>138371</v>
@@ -18343,33 +18082,33 @@
         <v>1749</v>
       </c>
       <c r="E20" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F20" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G20" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H20"/>
       <c r="I20"/>
       <c r="J20" t="s">
-        <v>3789</v>
+        <v>3781</v>
       </c>
       <c r="K20" t="s">
-        <v>3790</v>
+        <v>3782</v>
       </c>
       <c r="L20" t="s">
-        <v>3789</v>
+        <v>3781</v>
       </c>
       <c r="M20" t="s">
-        <v>3791</v>
+        <v>3783</v>
       </c>
       <c r="N20" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O20" t="s">
-        <v>3792</v>
+        <v>3784</v>
       </c>
       <c r="P20" t="n">
         <v>140059</v>
@@ -18389,33 +18128,33 @@
         <v>954</v>
       </c>
       <c r="E21" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F21" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G21" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H21"/>
       <c r="I21"/>
       <c r="J21" t="s">
-        <v>3793</v>
+        <v>3785</v>
       </c>
       <c r="K21" t="s">
-        <v>3794</v>
+        <v>3786</v>
       </c>
       <c r="L21" t="s">
-        <v>3793</v>
+        <v>3785</v>
       </c>
       <c r="M21" t="s">
-        <v>3795</v>
+        <v>3787</v>
       </c>
       <c r="N21" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O21" t="s">
-        <v>3796</v>
+        <v>3788</v>
       </c>
       <c r="P21" t="n">
         <v>141694</v>
@@ -18435,30 +18174,30 @@
         <v>873</v>
       </c>
       <c r="E22" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F22" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G22" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H22"/>
       <c r="I22"/>
       <c r="J22" t="s">
-        <v>3797</v>
+        <v>3789</v>
       </c>
       <c r="K22" t="s">
-        <v>3798</v>
+        <v>3790</v>
       </c>
       <c r="L22" t="s">
-        <v>3797</v>
+        <v>3789</v>
       </c>
       <c r="M22" t="s">
-        <v>3740</v>
+        <v>3732</v>
       </c>
       <c r="N22" t="s">
-        <v>3741</v>
+        <v>3733</v>
       </c>
       <c r="O22"/>
       <c r="P22" t="n">
@@ -18479,33 +18218,33 @@
         <v>2862</v>
       </c>
       <c r="E23" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F23" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G23" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H23"/>
       <c r="I23"/>
       <c r="J23" t="s">
-        <v>3799</v>
+        <v>3791</v>
       </c>
       <c r="K23" t="s">
-        <v>3800</v>
+        <v>3792</v>
       </c>
       <c r="L23" t="s">
-        <v>3799</v>
+        <v>3791</v>
       </c>
       <c r="M23" t="s">
-        <v>3801</v>
+        <v>3793</v>
       </c>
       <c r="N23" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O23" t="s">
-        <v>3802</v>
+        <v>3794</v>
       </c>
       <c r="P23" t="n">
         <v>146204</v>
@@ -18525,33 +18264,33 @@
         <v>666</v>
       </c>
       <c r="E24" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F24" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G24" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H24"/>
       <c r="I24"/>
       <c r="J24" t="s">
-        <v>3803</v>
+        <v>3795</v>
       </c>
       <c r="K24" t="s">
-        <v>3804</v>
+        <v>3796</v>
       </c>
       <c r="L24" t="s">
-        <v>3803</v>
+        <v>3795</v>
       </c>
       <c r="M24" t="s">
-        <v>3805</v>
+        <v>3797</v>
       </c>
       <c r="N24" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O24" t="s">
-        <v>3806</v>
+        <v>3798</v>
       </c>
       <c r="P24" t="n">
         <v>148570</v>
@@ -18571,33 +18310,33 @@
         <v>1092</v>
       </c>
       <c r="E25" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F25" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G25" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H25"/>
       <c r="I25"/>
       <c r="J25" t="s">
-        <v>3704</v>
+        <v>3696</v>
       </c>
       <c r="K25" t="s">
-        <v>3807</v>
+        <v>3799</v>
       </c>
       <c r="L25" t="s">
-        <v>3704</v>
+        <v>3696</v>
       </c>
       <c r="M25" t="s">
-        <v>3808</v>
+        <v>3800</v>
       </c>
       <c r="N25" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O25" t="s">
-        <v>3705</v>
+        <v>3697</v>
       </c>
       <c r="P25" t="n">
         <v>153382</v>
@@ -18617,33 +18356,33 @@
         <v>648</v>
       </c>
       <c r="E26" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F26" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G26" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H26"/>
       <c r="I26"/>
       <c r="J26" t="s">
-        <v>3688</v>
+        <v>3680</v>
       </c>
       <c r="K26" t="s">
-        <v>3809</v>
+        <v>3801</v>
       </c>
       <c r="L26" t="s">
-        <v>3688</v>
+        <v>3680</v>
       </c>
       <c r="M26" t="s">
-        <v>3761</v>
+        <v>3753</v>
       </c>
       <c r="N26" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O26" t="s">
-        <v>3690</v>
+        <v>3682</v>
       </c>
       <c r="P26" t="n">
         <v>154336</v>
@@ -18663,33 +18402,33 @@
         <v>267</v>
       </c>
       <c r="E27" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F27" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G27" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H27"/>
       <c r="I27"/>
       <c r="J27" t="s">
-        <v>3810</v>
+        <v>3802</v>
       </c>
       <c r="K27" t="s">
-        <v>3811</v>
+        <v>3803</v>
       </c>
       <c r="L27" t="s">
-        <v>3810</v>
+        <v>3802</v>
       </c>
       <c r="M27" t="s">
-        <v>3812</v>
+        <v>3804</v>
       </c>
       <c r="N27" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O27" t="s">
-        <v>3813</v>
+        <v>3805</v>
       </c>
       <c r="P27" t="n">
         <v>154963</v>
@@ -18709,33 +18448,33 @@
         <v>237</v>
       </c>
       <c r="E28" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F28" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G28" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H28"/>
       <c r="I28"/>
       <c r="J28" t="s">
-        <v>3814</v>
+        <v>3806</v>
       </c>
       <c r="K28" t="s">
-        <v>3815</v>
+        <v>3807</v>
       </c>
       <c r="L28" t="s">
-        <v>3814</v>
+        <v>3806</v>
       </c>
       <c r="M28" t="s">
-        <v>3816</v>
+        <v>3808</v>
       </c>
       <c r="N28" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O28" t="s">
-        <v>3817</v>
+        <v>3809</v>
       </c>
       <c r="P28" t="n">
         <v>155438</v>
@@ -18755,33 +18494,33 @@
         <v>999</v>
       </c>
       <c r="E29" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F29" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G29" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H29"/>
       <c r="I29"/>
       <c r="J29" t="s">
-        <v>3818</v>
+        <v>3810</v>
       </c>
       <c r="K29" t="s">
-        <v>3819</v>
+        <v>3811</v>
       </c>
       <c r="L29" t="s">
-        <v>3818</v>
+        <v>3810</v>
       </c>
       <c r="M29" t="s">
-        <v>3820</v>
+        <v>3812</v>
       </c>
       <c r="N29" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O29" t="s">
-        <v>3821</v>
+        <v>3813</v>
       </c>
       <c r="P29" t="n">
         <v>156608</v>
@@ -18801,30 +18540,30 @@
         <v>345</v>
       </c>
       <c r="E30" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F30" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G30" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H30"/>
       <c r="I30"/>
       <c r="J30" t="s">
-        <v>3822</v>
+        <v>3814</v>
       </c>
       <c r="K30" t="s">
-        <v>3823</v>
+        <v>3815</v>
       </c>
       <c r="L30" t="s">
-        <v>3822</v>
+        <v>3814</v>
       </c>
       <c r="M30" t="s">
-        <v>3740</v>
+        <v>3732</v>
       </c>
       <c r="N30" t="s">
-        <v>3741</v>
+        <v>3733</v>
       </c>
       <c r="O30"/>
       <c r="P30" t="n">
@@ -18845,30 +18584,30 @@
         <v>1836</v>
       </c>
       <c r="E31" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F31" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G31" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H31"/>
       <c r="I31"/>
       <c r="J31" t="s">
-        <v>3698</v>
+        <v>3690</v>
       </c>
       <c r="K31" t="s">
-        <v>3824</v>
+        <v>3816</v>
       </c>
       <c r="L31" t="s">
-        <v>3698</v>
+        <v>3690</v>
       </c>
       <c r="M31" t="s">
-        <v>3825</v>
+        <v>3817</v>
       </c>
       <c r="N31" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O31"/>
       <c r="P31" t="n">
@@ -18889,33 +18628,33 @@
         <v>1479</v>
       </c>
       <c r="E32" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F32" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G32" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H32"/>
       <c r="I32"/>
       <c r="J32" t="s">
-        <v>3826</v>
+        <v>3818</v>
       </c>
       <c r="K32" t="s">
-        <v>3827</v>
+        <v>3819</v>
       </c>
       <c r="L32" t="s">
-        <v>3826</v>
+        <v>3818</v>
       </c>
       <c r="M32" t="s">
-        <v>3828</v>
+        <v>3820</v>
       </c>
       <c r="N32" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O32" t="s">
-        <v>3829</v>
+        <v>3821</v>
       </c>
       <c r="P32" t="n">
         <v>161483</v>
@@ -18935,30 +18674,30 @@
         <v>267</v>
       </c>
       <c r="E33" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F33" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G33" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H33"/>
       <c r="I33"/>
       <c r="J33" t="s">
-        <v>3708</v>
+        <v>3700</v>
       </c>
       <c r="K33" t="s">
-        <v>3830</v>
+        <v>3822</v>
       </c>
       <c r="L33" t="s">
-        <v>3708</v>
+        <v>3700</v>
       </c>
       <c r="M33" t="s">
-        <v>3740</v>
+        <v>3732</v>
       </c>
       <c r="N33" t="s">
-        <v>3741</v>
+        <v>3733</v>
       </c>
       <c r="O33"/>
       <c r="P33" t="n">
@@ -18979,33 +18718,33 @@
         <v>123</v>
       </c>
       <c r="E34" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F34" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G34" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H34"/>
       <c r="I34"/>
       <c r="J34" t="s">
-        <v>3681</v>
+        <v>3673</v>
       </c>
       <c r="K34" t="s">
-        <v>3831</v>
+        <v>3823</v>
       </c>
       <c r="L34" t="s">
-        <v>3681</v>
+        <v>3673</v>
       </c>
       <c r="M34" t="s">
-        <v>3832</v>
+        <v>3824</v>
       </c>
       <c r="N34" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O34" t="s">
-        <v>3682</v>
+        <v>3674</v>
       </c>
       <c r="P34" t="n">
         <v>163006</v>
@@ -19025,30 +18764,30 @@
         <v>411</v>
       </c>
       <c r="E35" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F35" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G35" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H35"/>
       <c r="I35"/>
       <c r="J35" t="s">
-        <v>3833</v>
+        <v>3825</v>
       </c>
       <c r="K35" t="s">
-        <v>3834</v>
+        <v>3826</v>
       </c>
       <c r="L35" t="s">
-        <v>3833</v>
+        <v>3825</v>
       </c>
       <c r="M35" t="s">
-        <v>3740</v>
+        <v>3732</v>
       </c>
       <c r="N35" t="s">
-        <v>3741</v>
+        <v>3733</v>
       </c>
       <c r="O35"/>
       <c r="P35" t="n">
@@ -19069,33 +18808,33 @@
         <v>2229</v>
       </c>
       <c r="E36" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F36" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G36" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H36"/>
       <c r="I36"/>
       <c r="J36" t="s">
-        <v>3835</v>
+        <v>3827</v>
       </c>
       <c r="K36" t="s">
-        <v>3836</v>
+        <v>3828</v>
       </c>
       <c r="L36" t="s">
-        <v>3835</v>
+        <v>3827</v>
       </c>
       <c r="M36" t="s">
-        <v>3837</v>
+        <v>3829</v>
       </c>
       <c r="N36" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O36" t="s">
-        <v>3838</v>
+        <v>3830</v>
       </c>
       <c r="P36" t="n">
         <v>165225</v>
@@ -19115,33 +18854,33 @@
         <v>630</v>
       </c>
       <c r="E37" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F37" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G37" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H37"/>
       <c r="I37"/>
       <c r="J37" t="s">
-        <v>3839</v>
+        <v>3831</v>
       </c>
       <c r="K37" t="s">
-        <v>3840</v>
+        <v>3832</v>
       </c>
       <c r="L37" t="s">
-        <v>3839</v>
+        <v>3831</v>
       </c>
       <c r="M37" t="s">
-        <v>3841</v>
+        <v>3833</v>
       </c>
       <c r="N37" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O37" t="s">
-        <v>3842</v>
+        <v>3834</v>
       </c>
       <c r="P37" t="n">
         <v>167684</v>
@@ -19161,33 +18900,33 @@
         <v>1539</v>
       </c>
       <c r="E38" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F38" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G38" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H38"/>
       <c r="I38"/>
       <c r="J38" t="s">
-        <v>3843</v>
+        <v>3835</v>
       </c>
       <c r="K38" t="s">
-        <v>3844</v>
+        <v>3836</v>
       </c>
       <c r="L38" t="s">
-        <v>3843</v>
+        <v>3835</v>
       </c>
       <c r="M38" t="s">
-        <v>3845</v>
+        <v>3837</v>
       </c>
       <c r="N38" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O38" t="s">
-        <v>3846</v>
+        <v>3838</v>
       </c>
       <c r="P38" t="n">
         <v>171655</v>
@@ -19207,33 +18946,33 @@
         <v>491</v>
       </c>
       <c r="E39" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F39" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G39" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H39"/>
       <c r="I39"/>
       <c r="J39" t="s">
-        <v>3847</v>
+        <v>3839</v>
       </c>
       <c r="K39" t="s">
-        <v>3848</v>
+        <v>3840</v>
       </c>
       <c r="L39" t="s">
-        <v>3847</v>
+        <v>3839</v>
       </c>
       <c r="M39" t="s">
-        <v>3849</v>
+        <v>3841</v>
       </c>
       <c r="N39" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O39" t="s">
-        <v>3850</v>
+        <v>3842</v>
       </c>
       <c r="P39" t="n">
         <v>173195</v>
@@ -19253,33 +18992,33 @@
         <v>2613</v>
       </c>
       <c r="E40" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F40" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G40" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H40"/>
       <c r="I40"/>
       <c r="J40" t="s">
-        <v>3692</v>
+        <v>3684</v>
       </c>
       <c r="K40" t="s">
-        <v>3851</v>
+        <v>3843</v>
       </c>
       <c r="L40" t="s">
-        <v>3692</v>
+        <v>3684</v>
       </c>
       <c r="M40" t="s">
-        <v>3852</v>
+        <v>3844</v>
       </c>
       <c r="N40" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O40" t="s">
-        <v>3693</v>
+        <v>3685</v>
       </c>
       <c r="P40" t="n">
         <v>175132</v>
@@ -19299,33 +19038,33 @@
         <v>721</v>
       </c>
       <c r="E41" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F41" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G41" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H41"/>
       <c r="I41"/>
       <c r="J41" t="s">
-        <v>3702</v>
+        <v>3694</v>
       </c>
       <c r="K41" t="s">
-        <v>3853</v>
+        <v>3845</v>
       </c>
       <c r="L41" t="s">
-        <v>3702</v>
+        <v>3694</v>
       </c>
       <c r="M41" t="s">
-        <v>3854</v>
+        <v>3846</v>
       </c>
       <c r="N41" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O41" t="s">
-        <v>3703</v>
+        <v>3695</v>
       </c>
       <c r="P41" t="n">
         <v>177860</v>
@@ -19345,33 +19084,33 @@
         <v>6504</v>
       </c>
       <c r="E42" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F42" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G42" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H42"/>
       <c r="I42"/>
       <c r="J42" t="s">
-        <v>3855</v>
+        <v>3847</v>
       </c>
       <c r="K42" t="s">
-        <v>3856</v>
+        <v>3848</v>
       </c>
       <c r="L42" t="s">
-        <v>3855</v>
+        <v>3847</v>
       </c>
       <c r="M42" t="s">
-        <v>3857</v>
+        <v>3849</v>
       </c>
       <c r="N42" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O42" t="s">
-        <v>3858</v>
+        <v>3850</v>
       </c>
       <c r="P42" t="n">
         <v>182772</v>
@@ -19391,33 +19130,33 @@
         <v>3681</v>
       </c>
       <c r="E43" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F43" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G43" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H43"/>
       <c r="I43"/>
       <c r="J43" t="s">
-        <v>3700</v>
+        <v>3692</v>
       </c>
       <c r="K43" t="s">
-        <v>3859</v>
+        <v>3851</v>
       </c>
       <c r="L43" t="s">
-        <v>3700</v>
+        <v>3692</v>
       </c>
       <c r="M43" t="s">
-        <v>3860</v>
+        <v>3852</v>
       </c>
       <c r="N43" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O43" t="s">
-        <v>3701</v>
+        <v>3693</v>
       </c>
       <c r="P43" t="n">
         <v>188329</v>
@@ -19437,33 +19176,33 @@
         <v>1044</v>
       </c>
       <c r="E44" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F44" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G44" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H44"/>
       <c r="I44"/>
       <c r="J44" t="s">
-        <v>3861</v>
+        <v>3853</v>
       </c>
       <c r="K44" t="s">
-        <v>3862</v>
+        <v>3854</v>
       </c>
       <c r="L44" t="s">
-        <v>3861</v>
+        <v>3853</v>
       </c>
       <c r="M44" t="s">
-        <v>3863</v>
+        <v>3855</v>
       </c>
       <c r="N44" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O44" t="s">
-        <v>3864</v>
+        <v>3856</v>
       </c>
       <c r="P44" t="n">
         <v>191114</v>
@@ -19483,33 +19222,33 @@
         <v>1185</v>
       </c>
       <c r="E45" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F45" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G45" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H45"/>
       <c r="I45"/>
       <c r="J45" t="s">
-        <v>3865</v>
+        <v>3857</v>
       </c>
       <c r="K45" t="s">
-        <v>3866</v>
+        <v>3858</v>
       </c>
       <c r="L45" t="s">
-        <v>3865</v>
+        <v>3857</v>
       </c>
       <c r="M45" t="s">
-        <v>3867</v>
+        <v>3859</v>
       </c>
       <c r="N45" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O45" t="s">
-        <v>3868</v>
+        <v>3860</v>
       </c>
       <c r="P45" t="n">
         <v>192426</v>
@@ -19529,33 +19268,33 @@
         <v>1002</v>
       </c>
       <c r="E46" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F46" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G46" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H46"/>
       <c r="I46"/>
       <c r="J46" t="s">
-        <v>3869</v>
+        <v>3861</v>
       </c>
       <c r="K46" t="s">
-        <v>3870</v>
+        <v>3862</v>
       </c>
       <c r="L46" t="s">
-        <v>3869</v>
+        <v>3861</v>
       </c>
       <c r="M46" t="s">
-        <v>3871</v>
+        <v>3863</v>
       </c>
       <c r="N46" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O46" t="s">
-        <v>3872</v>
+        <v>3864</v>
       </c>
       <c r="P46" t="n">
         <v>193798</v>
@@ -19575,33 +19314,33 @@
         <v>2772</v>
       </c>
       <c r="E47" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F47" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G47" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H47"/>
       <c r="I47"/>
       <c r="J47" t="s">
-        <v>3873</v>
+        <v>3865</v>
       </c>
       <c r="K47" t="s">
-        <v>3874</v>
+        <v>3866</v>
       </c>
       <c r="L47" t="s">
-        <v>3873</v>
+        <v>3865</v>
       </c>
       <c r="M47" t="s">
-        <v>3875</v>
+        <v>3867</v>
       </c>
       <c r="N47" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O47" t="s">
-        <v>3876</v>
+        <v>3868</v>
       </c>
       <c r="P47" t="n">
         <v>195800</v>
@@ -19621,33 +19360,33 @@
         <v>1929</v>
       </c>
       <c r="E48" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F48" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G48" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H48"/>
       <c r="I48"/>
       <c r="J48" t="s">
-        <v>3877</v>
+        <v>3869</v>
       </c>
       <c r="K48" t="s">
-        <v>3878</v>
+        <v>3870</v>
       </c>
       <c r="L48" t="s">
-        <v>3877</v>
+        <v>3869</v>
       </c>
       <c r="M48" t="s">
-        <v>3879</v>
+        <v>3871</v>
       </c>
       <c r="N48" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O48" t="s">
-        <v>3880</v>
+        <v>3872</v>
       </c>
       <c r="P48" t="n">
         <v>198585</v>
@@ -19667,33 +19406,33 @@
         <v>633</v>
       </c>
       <c r="E49" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F49" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G49" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H49"/>
       <c r="I49"/>
       <c r="J49" t="s">
-        <v>3696</v>
+        <v>3688</v>
       </c>
       <c r="K49" t="s">
-        <v>3881</v>
+        <v>3873</v>
       </c>
       <c r="L49" t="s">
-        <v>3696</v>
+        <v>3688</v>
       </c>
       <c r="M49" t="s">
-        <v>3882</v>
+        <v>3874</v>
       </c>
       <c r="N49" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O49" t="s">
-        <v>3697</v>
+        <v>3689</v>
       </c>
       <c r="P49" t="n">
         <v>199862</v>
@@ -19713,33 +19452,33 @@
         <v>528</v>
       </c>
       <c r="E50" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F50" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G50" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H50"/>
       <c r="I50"/>
       <c r="J50" t="s">
-        <v>3883</v>
+        <v>3875</v>
       </c>
       <c r="K50" t="s">
-        <v>3884</v>
+        <v>3876</v>
       </c>
       <c r="L50" t="s">
-        <v>3883</v>
+        <v>3875</v>
       </c>
       <c r="M50" t="s">
-        <v>3885</v>
+        <v>3877</v>
       </c>
       <c r="N50" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O50" t="s">
-        <v>3886</v>
+        <v>3878</v>
       </c>
       <c r="P50" t="n">
         <v>200706</v>
@@ -19759,30 +19498,30 @@
         <v>333</v>
       </c>
       <c r="E51" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F51" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G51" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H51"/>
       <c r="I51"/>
       <c r="J51" t="s">
-        <v>3887</v>
+        <v>3879</v>
       </c>
       <c r="K51" t="s">
-        <v>3888</v>
+        <v>3880</v>
       </c>
       <c r="L51" t="s">
-        <v>3887</v>
+        <v>3879</v>
       </c>
       <c r="M51" t="s">
-        <v>3761</v>
+        <v>3753</v>
       </c>
       <c r="N51" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O51"/>
       <c r="P51" t="n">
@@ -19803,33 +19542,33 @@
         <v>4224</v>
       </c>
       <c r="E52" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F52" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G52" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H52"/>
       <c r="I52"/>
       <c r="J52" t="s">
-        <v>3686</v>
+        <v>3678</v>
       </c>
       <c r="K52" t="s">
-        <v>3889</v>
+        <v>3881</v>
       </c>
       <c r="L52" t="s">
-        <v>3686</v>
+        <v>3678</v>
       </c>
       <c r="M52" t="s">
-        <v>3890</v>
+        <v>3882</v>
       </c>
       <c r="N52" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O52" t="s">
-        <v>3687</v>
+        <v>3679</v>
       </c>
       <c r="P52" t="n">
         <v>203286</v>
@@ -19849,30 +19588,30 @@
         <v>384</v>
       </c>
       <c r="E53" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F53" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G53" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H53"/>
       <c r="I53"/>
       <c r="J53" t="s">
-        <v>3691</v>
+        <v>3683</v>
       </c>
       <c r="K53" t="s">
-        <v>3891</v>
+        <v>3883</v>
       </c>
       <c r="L53" t="s">
-        <v>3691</v>
+        <v>3683</v>
       </c>
       <c r="M53" t="s">
-        <v>3740</v>
+        <v>3732</v>
       </c>
       <c r="N53" t="s">
-        <v>3741</v>
+        <v>3733</v>
       </c>
       <c r="O53"/>
       <c r="P53" t="n">
@@ -19893,33 +19632,33 @@
         <v>1074</v>
       </c>
       <c r="E54" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F54" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G54" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H54"/>
       <c r="I54"/>
       <c r="J54" t="s">
-        <v>3892</v>
+        <v>3884</v>
       </c>
       <c r="K54" t="s">
-        <v>3893</v>
+        <v>3885</v>
       </c>
       <c r="L54" t="s">
-        <v>3892</v>
+        <v>3884</v>
       </c>
       <c r="M54" t="s">
-        <v>3894</v>
+        <v>3886</v>
       </c>
       <c r="N54" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O54" t="s">
-        <v>3895</v>
+        <v>3887</v>
       </c>
       <c r="P54" t="n">
         <v>207414</v>
@@ -19939,33 +19678,33 @@
         <v>1476</v>
       </c>
       <c r="E55" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F55" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G55" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H55"/>
       <c r="I55"/>
       <c r="J55" t="s">
-        <v>3896</v>
+        <v>3888</v>
       </c>
       <c r="K55" t="s">
-        <v>3897</v>
+        <v>3889</v>
       </c>
       <c r="L55" t="s">
-        <v>3896</v>
+        <v>3888</v>
       </c>
       <c r="M55" t="s">
-        <v>3898</v>
+        <v>3890</v>
       </c>
       <c r="N55" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O55" t="s">
-        <v>3899</v>
+        <v>3891</v>
       </c>
       <c r="P55" t="n">
         <v>208872</v>
@@ -19985,33 +19724,33 @@
         <v>510</v>
       </c>
       <c r="E56" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F56" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G56" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H56"/>
       <c r="I56"/>
       <c r="J56" t="s">
-        <v>3683</v>
+        <v>3675</v>
       </c>
       <c r="K56" t="s">
-        <v>3900</v>
+        <v>3892</v>
       </c>
       <c r="L56" t="s">
-        <v>3683</v>
+        <v>3675</v>
       </c>
       <c r="M56" t="s">
-        <v>3758</v>
+        <v>3750</v>
       </c>
       <c r="N56" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O56" t="s">
-        <v>3685</v>
+        <v>3677</v>
       </c>
       <c r="P56" t="n">
         <v>210168</v>
@@ -20031,33 +19770,33 @@
         <v>828</v>
       </c>
       <c r="E57" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F57" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G57" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H57"/>
       <c r="I57"/>
       <c r="J57" t="s">
-        <v>3714</v>
+        <v>3706</v>
       </c>
       <c r="K57" t="s">
-        <v>3901</v>
+        <v>3893</v>
       </c>
       <c r="L57" t="s">
-        <v>3714</v>
+        <v>3706</v>
       </c>
       <c r="M57" t="s">
-        <v>3902</v>
+        <v>3894</v>
       </c>
       <c r="N57" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O57" t="s">
-        <v>3715</v>
+        <v>3707</v>
       </c>
       <c r="P57" t="n">
         <v>211132</v>
@@ -20077,33 +19816,33 @@
         <v>1833</v>
       </c>
       <c r="E58" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F58" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G58" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H58"/>
       <c r="I58"/>
       <c r="J58" t="s">
-        <v>3903</v>
+        <v>3895</v>
       </c>
       <c r="K58" t="s">
-        <v>3904</v>
+        <v>3896</v>
       </c>
       <c r="L58" t="s">
-        <v>3903</v>
+        <v>3895</v>
       </c>
       <c r="M58" t="s">
-        <v>3905</v>
+        <v>3897</v>
       </c>
       <c r="N58" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O58" t="s">
-        <v>3906</v>
+        <v>3898</v>
       </c>
       <c r="P58" t="n">
         <v>212845</v>
@@ -20123,30 +19862,30 @@
         <v>309</v>
       </c>
       <c r="E59" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F59" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G59" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H59"/>
       <c r="I59"/>
       <c r="J59" t="s">
-        <v>3907</v>
+        <v>3899</v>
       </c>
       <c r="K59" t="s">
-        <v>3908</v>
+        <v>3900</v>
       </c>
       <c r="L59" t="s">
-        <v>3907</v>
+        <v>3899</v>
       </c>
       <c r="M59" t="s">
-        <v>3909</v>
+        <v>3901</v>
       </c>
       <c r="N59" t="s">
-        <v>3741</v>
+        <v>3733</v>
       </c>
       <c r="O59"/>
       <c r="P59" t="n">
@@ -20167,30 +19906,30 @@
         <v>669</v>
       </c>
       <c r="E60" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F60" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G60" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H60"/>
       <c r="I60"/>
       <c r="J60" t="s">
-        <v>3910</v>
+        <v>3902</v>
       </c>
       <c r="K60" t="s">
-        <v>3911</v>
+        <v>3903</v>
       </c>
       <c r="L60" t="s">
-        <v>3910</v>
+        <v>3902</v>
       </c>
       <c r="M60" t="s">
-        <v>3740</v>
+        <v>3732</v>
       </c>
       <c r="N60" t="s">
-        <v>3741</v>
+        <v>3733</v>
       </c>
       <c r="O60"/>
       <c r="P60" t="n">
@@ -20211,33 +19950,33 @@
         <v>1452</v>
       </c>
       <c r="E61" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F61" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G61" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H61"/>
       <c r="I61"/>
       <c r="J61" t="s">
-        <v>3912</v>
+        <v>3904</v>
       </c>
       <c r="K61" t="s">
-        <v>3913</v>
+        <v>3905</v>
       </c>
       <c r="L61" t="s">
-        <v>3912</v>
+        <v>3904</v>
       </c>
       <c r="M61" t="s">
-        <v>3816</v>
+        <v>3808</v>
       </c>
       <c r="N61" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O61" t="s">
-        <v>3914</v>
+        <v>3906</v>
       </c>
       <c r="P61" t="n">
         <v>215720</v>
@@ -20257,33 +19996,33 @@
         <v>1545</v>
       </c>
       <c r="E62" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F62" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G62" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H62"/>
       <c r="I62"/>
       <c r="J62" t="s">
-        <v>3915</v>
+        <v>3907</v>
       </c>
       <c r="K62" t="s">
-        <v>3916</v>
+        <v>3908</v>
       </c>
       <c r="L62" t="s">
-        <v>3915</v>
+        <v>3907</v>
       </c>
       <c r="M62" t="s">
-        <v>3917</v>
+        <v>3909</v>
       </c>
       <c r="N62" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O62" t="s">
-        <v>3918</v>
+        <v>3910</v>
       </c>
       <c r="P62" t="n">
         <v>217469</v>
@@ -20303,33 +20042,33 @@
         <v>1692</v>
       </c>
       <c r="E63" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F63" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G63" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H63"/>
       <c r="I63"/>
       <c r="J63" t="s">
-        <v>3919</v>
+        <v>3911</v>
       </c>
       <c r="K63" t="s">
-        <v>3920</v>
+        <v>3912</v>
       </c>
       <c r="L63" t="s">
-        <v>3919</v>
+        <v>3911</v>
       </c>
       <c r="M63" t="s">
-        <v>3921</v>
+        <v>3913</v>
       </c>
       <c r="N63" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O63" t="s">
-        <v>3922</v>
+        <v>3914</v>
       </c>
       <c r="P63" t="n">
         <v>219222</v>
@@ -20349,33 +20088,33 @@
         <v>2772</v>
       </c>
       <c r="E64" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F64" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G64" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H64"/>
       <c r="I64"/>
       <c r="J64" t="s">
-        <v>3923</v>
+        <v>3915</v>
       </c>
       <c r="K64" t="s">
-        <v>3924</v>
+        <v>3916</v>
       </c>
       <c r="L64" t="s">
-        <v>3923</v>
+        <v>3915</v>
       </c>
       <c r="M64" t="s">
-        <v>3925</v>
+        <v>3917</v>
       </c>
       <c r="N64" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O64" t="s">
-        <v>3926</v>
+        <v>3918</v>
       </c>
       <c r="P64" t="n">
         <v>221842</v>
@@ -20395,33 +20134,33 @@
         <v>777</v>
       </c>
       <c r="E65" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F65" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G65" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H65"/>
       <c r="I65"/>
       <c r="J65" t="s">
-        <v>3927</v>
+        <v>3919</v>
       </c>
       <c r="K65" t="s">
-        <v>3928</v>
+        <v>3920</v>
       </c>
       <c r="L65" t="s">
-        <v>3927</v>
+        <v>3919</v>
       </c>
       <c r="M65" t="s">
-        <v>3929</v>
+        <v>3921</v>
       </c>
       <c r="N65" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O65" t="s">
-        <v>3930</v>
+        <v>3922</v>
       </c>
       <c r="P65" t="n">
         <v>223842</v>
@@ -20441,33 +20180,33 @@
         <v>336</v>
       </c>
       <c r="E66" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F66" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G66" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H66"/>
       <c r="I66"/>
       <c r="J66" t="s">
-        <v>3694</v>
+        <v>3686</v>
       </c>
       <c r="K66" t="s">
-        <v>3931</v>
+        <v>3923</v>
       </c>
       <c r="L66" t="s">
-        <v>3694</v>
+        <v>3686</v>
       </c>
       <c r="M66" t="s">
-        <v>3932</v>
+        <v>3924</v>
       </c>
       <c r="N66" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O66" t="s">
-        <v>3695</v>
+        <v>3687</v>
       </c>
       <c r="P66" t="n">
         <v>224566</v>
@@ -20487,30 +20226,30 @@
         <v>1896</v>
       </c>
       <c r="E67" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F67" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G67" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H67"/>
       <c r="I67"/>
       <c r="J67" t="s">
-        <v>3933</v>
+        <v>3925</v>
       </c>
       <c r="K67" t="s">
-        <v>3934</v>
+        <v>3926</v>
       </c>
       <c r="L67" t="s">
-        <v>3933</v>
+        <v>3925</v>
       </c>
       <c r="M67" t="s">
-        <v>3761</v>
+        <v>3753</v>
       </c>
       <c r="N67" t="s">
-        <v>3741</v>
+        <v>3733</v>
       </c>
       <c r="O67"/>
       <c r="P67" t="n">
@@ -20531,33 +20270,33 @@
         <v>474</v>
       </c>
       <c r="E68" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F68" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G68" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H68"/>
       <c r="I68"/>
       <c r="J68" t="s">
-        <v>3935</v>
+        <v>3927</v>
       </c>
       <c r="K68" t="s">
-        <v>3936</v>
+        <v>3928</v>
       </c>
       <c r="L68" t="s">
-        <v>3935</v>
+        <v>3927</v>
       </c>
       <c r="M68" t="s">
-        <v>3937</v>
+        <v>3929</v>
       </c>
       <c r="N68" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O68" t="s">
-        <v>3938</v>
+        <v>3930</v>
       </c>
       <c r="P68" t="n">
         <v>228554</v>
@@ -20577,33 +20316,33 @@
         <v>1695</v>
       </c>
       <c r="E69" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F69" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G69" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H69"/>
       <c r="I69"/>
       <c r="J69" t="s">
-        <v>3939</v>
+        <v>3931</v>
       </c>
       <c r="K69" t="s">
-        <v>3940</v>
+        <v>3932</v>
       </c>
       <c r="L69" t="s">
-        <v>3939</v>
+        <v>3931</v>
       </c>
       <c r="M69" t="s">
-        <v>3941</v>
+        <v>3933</v>
       </c>
       <c r="N69" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O69" t="s">
-        <v>3942</v>
+        <v>3934</v>
       </c>
       <c r="P69" t="n">
         <v>230157</v>
@@ -20623,33 +20362,33 @@
         <v>1464</v>
       </c>
       <c r="E70" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F70" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G70" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H70"/>
       <c r="I70"/>
       <c r="J70" t="s">
-        <v>3943</v>
+        <v>3935</v>
       </c>
       <c r="K70" t="s">
-        <v>3944</v>
+        <v>3936</v>
       </c>
       <c r="L70" t="s">
-        <v>3943</v>
+        <v>3935</v>
       </c>
       <c r="M70" t="s">
-        <v>3945</v>
+        <v>3937</v>
       </c>
       <c r="N70" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O70" t="s">
-        <v>3946</v>
+        <v>3938</v>
       </c>
       <c r="P70" t="n">
         <v>232232</v>
@@ -20669,33 +20408,33 @@
         <v>3198</v>
       </c>
       <c r="E71" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F71" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G71" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H71"/>
       <c r="I71"/>
       <c r="J71" t="s">
-        <v>3947</v>
+        <v>3939</v>
       </c>
       <c r="K71" t="s">
-        <v>3948</v>
+        <v>3940</v>
       </c>
       <c r="L71" t="s">
-        <v>3947</v>
+        <v>3939</v>
       </c>
       <c r="M71" t="s">
-        <v>3949</v>
+        <v>3941</v>
       </c>
       <c r="N71" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O71" t="s">
-        <v>3950</v>
+        <v>3942</v>
       </c>
       <c r="P71" t="n">
         <v>234724</v>
@@ -20715,33 +20454,33 @@
         <v>1563</v>
       </c>
       <c r="E72" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F72" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G72" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H72"/>
       <c r="I72"/>
       <c r="J72" t="s">
-        <v>3951</v>
+        <v>3943</v>
       </c>
       <c r="K72" t="s">
-        <v>3952</v>
+        <v>3944</v>
       </c>
       <c r="L72" t="s">
-        <v>3951</v>
+        <v>3943</v>
       </c>
       <c r="M72" t="s">
-        <v>3953</v>
+        <v>3945</v>
       </c>
       <c r="N72" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O72" t="s">
-        <v>3954</v>
+        <v>3946</v>
       </c>
       <c r="P72" t="n">
         <v>237995</v>
@@ -20761,33 +20500,33 @@
         <v>957</v>
       </c>
       <c r="E73" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F73" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G73" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H73"/>
       <c r="I73"/>
       <c r="J73" t="s">
-        <v>3955</v>
+        <v>3947</v>
       </c>
       <c r="K73" t="s">
-        <v>3956</v>
+        <v>3948</v>
       </c>
       <c r="L73" t="s">
-        <v>3955</v>
+        <v>3947</v>
       </c>
       <c r="M73" t="s">
-        <v>3957</v>
+        <v>3949</v>
       </c>
       <c r="N73" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O73" t="s">
-        <v>3958</v>
+        <v>3950</v>
       </c>
       <c r="P73" t="n">
         <v>239533</v>
@@ -20807,33 +20546,33 @@
         <v>441</v>
       </c>
       <c r="E74" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F74" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G74" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H74"/>
       <c r="I74"/>
       <c r="J74" t="s">
-        <v>3959</v>
+        <v>3951</v>
       </c>
       <c r="K74" t="s">
-        <v>3960</v>
+        <v>3952</v>
       </c>
       <c r="L74" t="s">
-        <v>3959</v>
+        <v>3951</v>
       </c>
       <c r="M74" t="s">
-        <v>3758</v>
+        <v>3750</v>
       </c>
       <c r="N74" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O74" t="s">
-        <v>3961</v>
+        <v>3953</v>
       </c>
       <c r="P74" t="n">
         <v>240323</v>
@@ -20853,33 +20592,33 @@
         <v>1548</v>
       </c>
       <c r="E75" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F75" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G75" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H75"/>
       <c r="I75"/>
       <c r="J75" t="s">
-        <v>3962</v>
+        <v>3954</v>
       </c>
       <c r="K75" t="s">
-        <v>3963</v>
+        <v>3955</v>
       </c>
       <c r="L75" t="s">
-        <v>3962</v>
+        <v>3954</v>
       </c>
       <c r="M75" t="s">
-        <v>3964</v>
+        <v>3956</v>
       </c>
       <c r="N75" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O75" t="s">
-        <v>3965</v>
+        <v>3957</v>
       </c>
       <c r="P75" t="n">
         <v>241578</v>
@@ -20899,33 +20638,33 @@
         <v>3996</v>
       </c>
       <c r="E76" t="s">
-        <v>3737</v>
+        <v>3729</v>
       </c>
       <c r="F76" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G76" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H76"/>
       <c r="I76"/>
       <c r="J76" t="s">
-        <v>3716</v>
+        <v>3708</v>
       </c>
       <c r="K76" t="s">
-        <v>3966</v>
+        <v>3958</v>
       </c>
       <c r="L76" t="s">
-        <v>3716</v>
+        <v>3708</v>
       </c>
       <c r="M76" t="s">
-        <v>3967</v>
+        <v>3959</v>
       </c>
       <c r="N76" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O76" t="s">
-        <v>3717</v>
+        <v>3709</v>
       </c>
       <c r="P76" t="n">
         <v>244586</v>
@@ -20945,33 +20684,33 @@
         <v>948</v>
       </c>
       <c r="E77" t="s">
-        <v>3726</v>
+        <v>3718</v>
       </c>
       <c r="F77" t="s">
-        <v>3727</v>
+        <v>3719</v>
       </c>
       <c r="G77" t="s">
-        <v>3725</v>
+        <v>3717</v>
       </c>
       <c r="H77"/>
       <c r="I77"/>
       <c r="J77" t="s">
-        <v>3968</v>
+        <v>3960</v>
       </c>
       <c r="K77" t="s">
-        <v>3969</v>
+        <v>3961</v>
       </c>
       <c r="L77" t="s">
-        <v>3968</v>
+        <v>3960</v>
       </c>
       <c r="M77" t="s">
-        <v>3970</v>
+        <v>3962</v>
       </c>
       <c r="N77" t="s">
-        <v>3731</v>
+        <v>3723</v>
       </c>
       <c r="O77" t="s">
-        <v>3971</v>
+        <v>3963</v>
       </c>
       <c r="P77" t="n">
         <v>247436</v>
